--- a/docs/Mens_Wellness_Content_Roadmap.xlsx
+++ b/docs/Mens_Wellness_Content_Roadmap.xlsx
@@ -2800,7 +2800,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Thủ dâm hay xuất tinh không làm suy giảm nồng độ testosterone nền tảng dài hạn của nam giới. Hiện tượng testosterone tăng vọt vào ngày thứ 7 kiêng cữ chỉ là một đỉnh điều hòa tạm thời trước khi tụt về mức bình thường. Ngược lại, xuất tinh đều đặn $\ge 21$ lần/tháng được chứng minh lâm sàng giúp giảm 31% nguy cơ ung thư tuyến tiền liệt.</t>
+          <t>Thủ dâm hay xuất tinh không làm suy giảm nồng độ testosterone nền tảng dài hạn của nam giới. Hiện tượng testosterone tăng vọt vào ngày thứ 7 kiêng cữ chỉ là một đỉnh điều hòa tạm thời trước khi tụt về mức bình thường. Ngược lại, xuất tinh đều đặn ≥ 21 lần/tháng được chứng minh lâm sàng giúp giảm 31% nguy cơ ung thư tuyến tiền liệt.</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3116,6 +3116,8 @@
         <v>32</v>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>

--- a/docs/Mens_Wellness_Content_Roadmap.xlsx
+++ b/docs/Mens_Wellness_Content_Roadmap.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Content Roadmap" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Overview" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Roadmap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -408,7 +408,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -2986,7 +2986,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -3116,8 +3116,6 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>

--- a/docs/Mens_Wellness_Content_Roadmap.xlsx
+++ b/docs/Mens_Wellness_Content_Roadmap.xlsx
@@ -5,15 +5,20 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Roadmap" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reviewed_Content" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Register" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reviewed_Content'!$A$1:$H$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Source_Register'!$A$1:$F$29</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -48,8 +53,16 @@
       <b val="1"/>
       <color rgb="00047857"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +91,11 @@
         <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00184E52"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -86,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,6 +135,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -408,7 +435,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -512,17 +539,17 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Can Your Diet Affect Testosterone?</t>
+          <t>Diet and testosterone: adequacy before boosters</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Chế độ ăn ảnh hưởng testosterone thế nào?</t>
+          <t>Ăn uống và testosterone: ưu tiên đủ chất, tránh lời hứa tăng hormone</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Năng lượng, chất béo, cân nặng và giới hạn bằng chứng</t>
+          <t>Dinh dưỡng kém và thiếu năng lượng có thể ảnh hưởng sức khỏe sinh sản, nhưng không có một món ăn bảo đảm tăng testosterone ở người đã đủ chất.</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
@@ -537,17 +564,17 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/29562364/</t>
+          <t>https://www.who.int/news-room/fact-sheets/detail/healthy-diet</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J2" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_NUT_01)</t>
+          <t>Revised — MW_NUT_01; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -557,22 +584,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Chế Độ Ăn &amp; Testosterone: Khoa Học Về Chất Béo, Calo &amp; Sự Thần Thoại Hóa Thực Phẩm</t>
+          <t>Ăn uống và testosterone: ưu tiên đủ chất, tránh lời hứa tăng hormone</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Diet and Testosterone: The Science of Lipids, Energy Balance &amp; Food Myths</t>
+          <t>Diet and testosterone: adequacy before boosters</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Testosterone được tổng hợp từ cholesterol và lipid. Duy trì lượng chất béo lành mạnh ở mức 25%–35% tổng năng lượng, tránh thâm hụt calo quá 20% và đảm bảo đủ kẽm, magie cùng năng lượng sẵn có là nền tảng cốt lõi để giữ trục HPTA hoạt động bền bỉ.</t>
+          <t>Duy trì bữa ăn đa dạng, đủ năng lượng cho sinh hoạt và tập luyện. Nếu đang ăn kiêng quá mức, xem lại mục tiêu với chuyên gia. Khi có triệu chứng kéo dài, trao đổi về đánh giá nguyên nhân trước khi mua sản phẩm tăng T.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Daily Caloric Balance, Macronutrient Split &amp; Androgen Profile</t>
+          <t>Diet and testosterone: adequacy before boosters (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -589,17 +616,17 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>The Mediterranean Diet and Men’s Sexual Health</t>
+          <t>Mediterranean-style eating and men's health</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Chế độ ăn Địa Trung Hải và sức khỏe tình dục</t>
+          <t>Ăn kiểu Địa Trung Hải: một cách xây bữa ăn lành mạnh</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Sức khỏe chuyển hóa và erectile function</t>
+          <t>Mô hình ăn nhiều rau, đậu, ngũ cốc nguyên hạt, cá và chất béo không bão hòa phù hợp nhiều nguyên tắc ăn lành mạnh.</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -614,17 +641,17 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/15213207/</t>
+          <t>https://www.who.int/news-room/fact-sheets/detail/healthy-diet</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J3" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_NUT_02)</t>
+          <t>Revised — MW_NUT_02; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -634,22 +661,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Chế Độ Ăn Địa Trung Hải: Tấm Lá Chắn Nội Mô Cho Chức Năng Cương &amp; Tim Mạch Nam Giới</t>
+          <t>Ăn kiểu Địa Trung Hải: một cách xây bữa ăn lành mạnh</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The Mediterranean Diet: Endothelial Shield for Erectile Function &amp; Longevity</t>
+          <t>Mediterranean-style eating and men's health</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Động mạch hang dương vật là cửa sổ báo hiệu sớm nhất của toàn bộ hệ tuần hoàn. Chế độ ăn Địa Trung Hải bảo vệ lớp nội mô mạch máu bằng cách kích thích enzyme eNOS sản sinh Nitric Oxide, cải thiện độ đàn hồi vi mạch và giảm phản ứng viêm toàn thân.</t>
+          <t>Bắt đầu bằng một thay đổi dễ duy trì: thêm đậu hoặc rau vào bữa, đổi một phần thịt chế biến sang cá hoặc đạm thực vật. Chọn món quen tại địa phương; không cần mua thực phẩm nhập khẩu hay uống rượu vang để theo mô hình này.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Vascular Endothelial Function, Nitric Oxide Synthesis &amp; RHR</t>
+          <t>Mediterranean-style eating and men's health (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -666,17 +693,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>How Much Protein Do Men Really Need?</t>
+          <t>Protein needs for resistance training</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Nam giới thực sự cần bao nhiêu protein?</t>
+          <t>Cần bao nhiêu protein khi tập sức mạnh?</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Protein theo mục tiêu và cân nặng</t>
+          <t>Protein hỗ trợ thích nghi khi kết hợp tập sức mạnh.</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -696,12 +723,12 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J4" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_NUT_03)</t>
+          <t>Revised — MW_NUT_03; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -711,22 +738,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Nam Giới Cần Bao Nhiêu Protein? Tối Ưu Tổng Hợp Cơ Bắp, Thận &amp; Cân Bằng Nội Tiết</t>
+          <t>Cần bao nhiêu protein khi tập sức mạnh?</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Protein Requirements for Men: Optimizing Muscle Protein Synthesis, Renal Health &amp; Hormones</t>
+          <t>Protein needs for resistance training</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Ngưỡng nạp protein tối ưu cho nam giới vận động là 1.6 đến 2.2 g/kg thể trọng mỗi ngày. Chia đều thành 3–4 bữa, mỗi bữa chứa 2.5–3g Leucine là cách hiệu quả nhất để kích hoạt tín hiệu tổng hợp protein cơ bắp (mTOR) mà không gây hại cho thận ở người khỏe mạnh.</t>
+          <t>Ví dụ, 70 kg nhân 1,6 tương đương khoảng 112 g protein mỗi ngày. Có thể chia giữa các bữa từ cá, trứng, sữa, đậu hoặc thực phẩm phù hợp. Kiểm tra tổng khẩu phần trước khi mua bột protein.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Muscle Protein Synthesis, Leucine Threshold &amp; Day Strain</t>
+          <t>Protein needs for resistance training (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -743,17 +770,17 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Does Alcohol Affect Testosterone and Recovery?</t>
+          <t>Alcohol and recovery</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Rượu bia ảnh hưởng testosterone và phục hồi?</t>
+          <t>Rượu bia và phục hồi: giảm rủi ro thay vì tìm liều có lợi</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Rượu, giấc ngủ, hormone</t>
+          <t>Rượu có thể khiến dễ buồn ngủ nhưng không phải cách tạo giấc ngủ tốt; tác động phụ thuộc lượng uống và bối cảnh.</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -768,17 +795,17 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/24533518/</t>
+          <t>https://www.who.int/news-room/fact-sheets/detail/alcohol</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J5" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_NUT_04)</t>
+          <t>Revised — MW_NUT_04; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -788,22 +815,22 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Rượu Bia Tàn Phá Phục Hồi Thế Nào? Cơ Chế Ức Chế Hormone T &amp; Đứt Gãy Giấc Ngủ REM</t>
+          <t>Rượu bia và phục hồi: giảm rủi ro thay vì tìm liều có lợi</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Alcohol, Testosterone &amp; Recovery: Acute Leydig Cell Suppression &amp; REM Fragmentation</t>
+          <t>Alcohol and recovery</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Chất cồn là độc tố chuyển hóa ưu tiên đào thải. Nó làm sụt giảm 20%–40% testosterone sau các buổi nhậu, ức chế quá trình tổng hợp cơ bắp và cắt cụt giấc ngủ REM. Nếu uống rượu, hãy cách giờ đi ngủ ít nhất 4 tiếng và bù nước kèm điện giải.</t>
+          <t>Nếu muốn xem tác động cá nhân, thử giảm hoặc tránh uống và ghi chất lượng ngủ, cảm giác sáng hôm sau cùng lịch tập. Không dùng đồ uống có cồn như phần bắt buộc của phục hồi hoặc chế độ ăn lành mạnh.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Overnight RHR, Sleep Architecture (REM Suppression) &amp; Recovery Score</t>
+          <t>Alcohol and recovery (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -820,17 +847,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Zinc, Vitamin D, and Male Hormones</t>
+          <t>Zinc and vitamin D: needs rather than hormone promises</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Kẽm, vitamin D và hormone nam giới</t>
+          <t>Kẽm và vitamin D: bổ sung theo nhu cầu, không theo lời hứa tăng T</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Thiếu hụt so với bổ sung không cần thiết</t>
+          <t>Kẽm và vitamin D có vai trò sinh học thiết yếu.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -845,17 +872,17 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/8875519/</t>
+          <t>https://ods.od.nih.gov/factsheets/Zinc-HealthProfessional/</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_NUT_05)</t>
+          <t>Revised — MW_NUT_05; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -865,22 +892,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Kẽm &amp; Vitamin D: Vi Chất Tối Cần Thiết Cho Tế Bào Leydig &amp; Thụ Thể Androgen</t>
+          <t>Kẽm và vitamin D: bổ sung theo nhu cầu, không theo lời hứa tăng T</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Zinc and Vitamin D: Essential Micronutrients for Leydig Cell Function &amp; Androgen Receptors</t>
+          <t>Zinc and vitamin D: needs rather than hormone promises</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Kẽm là thành phần cốt lõi của hơn 300 enzyme và cấu trúc ngón tay kẽm (Zinc Fingers) của thụ thể Androgen; trong khi Vitamin D hoạt động như một hormone tiền chất kích hoạt thụ thể VDR tại tinh hoàn. Bổ sung 15–30mg Kẽm Bisglycinate và 2.000–4.000 IU Vitamin D3 hàng ngày là chiến lược phục hồi nội tiết đơn giản và hiệu quả nhất.</t>
+          <t>Kiểm tra thực phẩm và mọi viên đang dùng để tránh cộng dồn. Nếu nghi thiếu hoặc có yếu tố nguy cơ, hỏi bác sĩ về đánh giá và liều phù hợp. Không dùng một phác đồ tăng hormone từ mạng thay cho chẩn đoán.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Leydig Cell Steroidogenesis, VDR Nuclear Receptors &amp; Zinc Homeostasis</t>
+          <t>Zinc and vitamin D: needs rather than hormone promises (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -897,17 +924,17 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Nutrition for Better Sperm Health</t>
+          <t>Nutrition and sperm health: evidence limits</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Dinh dưỡng và sức khỏe tinh trùng</t>
+          <t>Dinh dưỡng và chất lượng tinh trùng: hiểu giới hạn bằng chứng</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Chế độ ăn và các thông số tinh dịch</t>
+          <t>Chế độ ăn là một phần sức khỏe sinh sản, nhưng chỉ số tinh dịch không đồng nghĩa chắc chắn có thai hoặc sinh con.</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -922,17 +949,17 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/28333357/</t>
+          <t>https://integration.asrm.org/practice-guidance/practice-committee-documents/diagnosis-and-treatment-of-infertility-in-men-aua-asrm-guideline-part2/</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_NUT_06)</t>
+          <t>Revised — MW_NUT_06; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -942,22 +969,22 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Dinh Dưỡng Nâng Cao Chất Lượng Tinh Trùng: Bảo Vệ DNA &amp; Tăng Khả Năng Vận Động</t>
+          <t>Dinh dưỡng và chất lượng tinh trùng: hiểu giới hạn bằng chứng</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Nutritional Protocols for Sperm Quality: Protecting DNA Fragmentation &amp; Motility</t>
+          <t>Nutrition and sperm health: evidence limits</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Chu kỳ sinh tinh kéo dài trung bình 74 ngày cộng thêm 14 ngày trưởng thành tại mào tinh hoàn. Tinh trùng cực kỳ dễ bị tổn thương bởi các gốc tự do ROS gây đứt gãy DNA. Bổ sung CoQ10, L-Carnitine, Lycopene và Omega-3 EPA/DHA trong tối thiểu 90 ngày giúp cải thiện rõ rệt mật độ, độ dị động và hình thái tinh trùng theo tiêu chuẩn WHO.</t>
+          <t>Ưu tiên ăn đa dạng, tránh hút thuốc và trao đổi về bệnh, thuốc cùng kế hoạch có con. Nếu đang khó có thai, đánh giá cả hai phía thay vì chỉ tự mua viên bổ tinh trùng; kiểm tra thành phần nếu đang dùng nhiều sản phẩm.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Spermatogenic Cycle (74 Days), DNA Fragmentation &amp; Semen Parameters</t>
+          <t>Nutrition and sperm health: evidence limits (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -974,17 +1001,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Does Intermittent Fasting Affect Male Hormones?</t>
+          <t>Intermittent fasting and male hormones</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Nhịn ăn gián đoạn ảnh hưởng hormone nam?</t>
+          <t>Nhịn ăn gián đoạn và hormone nam: còn nhiều điều chưa chắc chắn</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Cân nặng, chuyển hóa, testosterone</t>
+          <t>Các thử nghiệm ở người về nhịn ăn và hormone sinh sản còn ít, thời gian và nhóm tham gia khác nhau.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -999,17 +1026,17 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/27737674/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35684143/</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_NUT_07)</t>
+          <t>Revised — MW_NUT_07; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1019,22 +1046,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Nhịn Ăn Gián Đoạn (IF) &amp; Nội Tiết Tố Nam: Lợi Ích Nhạy Insulin So Với Rủi Ro Tụt Testosterone</t>
+          <t>Nhịn ăn gián đoạn và hormone nam: còn nhiều điều chưa chắc chắn</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Intermittent Fasting &amp; Male Hormones: Insulin Sensitivity Gains vs. Androgen Drops</t>
+          <t>Intermittent fasting and male hormones</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Nhịn ăn gián đoạn 16/8 là công cụ tuyệt vời để giảm mỡ nội tạng và tăng độ nhạy insulin ở nam giới thừa cân (giúp gián tiếp tăng testosterone do giảm enzyme aromatase). Nhưng ở nam giới đã có thân hình săn chắc (body fat &lt;12%) hoặc tập tạ nặng, nhịn ăn quá 16 tiếng sẽ kích hoạt tín hiệu thiếu năng lượng sẵn có, làm tụt Free T và tăng Cortisol.</t>
+          <t>Nếu thử, chọn lịch vẫn cho phép ăn đủ, tập và ngủ thoải mái. Theo dõi mức đói, mệt, hiệu suất và khả năng duy trì. Người dùng thuốc tiểu đường, có bệnh hoặc tiền sử rối loạn ăn uống nên được tư vấn riêng.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Insulin Sensitivity, Growth Hormone Pulsatility &amp; LH/Testosterone</t>
+          <t>Intermittent fasting and male hormones (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1078,17 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Hydration, Energy, and Exercise Performance</t>
+          <t>Hydration during activity</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Nước, năng lượng và hiệu suất vận động</t>
+          <t>Bù nước khi vận động: đáp ứng nhu cầu thay vì ép một công thức</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Mất nước và hiệu suất tập luyện</t>
+          <t>Nhu cầu dịch phụ thuộc thời tiết, thời gian vận động, mồ hôi, thức ăn và bệnh nền.</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -1076,17 +1103,17 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/17277604/</t>
+          <t>https://www.nhs.uk/conditions/dehydration/</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_NUT_08)</t>
+          <t>Revised — MW_NUT_08; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1096,22 +1123,22 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Bù Nước &amp; Hiệu Suất Thể Lực: Ảnh Hưởng Của Mất Nước 2% Lên Thể Tích Huyết Tương &amp; Nhịp Tim</t>
+          <t>Bù nước khi vận động: đáp ứng nhu cầu thay vì ép một công thức</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Hydration Dynamics: How a 2% Body Water Deficit Spikes Heart Rate &amp; Derails Muscle Work</t>
+          <t>Hydration during activity</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Mất nước 2% làm giảm thể tích huyết tương, khiến máu bị cô đặc và giảm thể tích tống máu của tim (Stroke Volume). Để bù lại, tim phải đập thêm 3–7 nhịp mỗi phút (Cardiac Drift) cho cùng một cường độ vận động. Hãy uống 35–45ml nước/kg thể trọng mỗi ngày và bổ sung 500mg Natri kèm điện giải trong các buổi tập kéo dài trên 60 phút.</t>
+          <t>Mang nước khi vận động và điều chỉnh theo khát, điều kiện cùng hướng dẫn riêng nếu có. Với buổi dài hoặc nóng, có thể cần kế hoạch bổ sung dịch và điện giải phù hợp; tránh ép uống lượng lớn chỉ để đạt mục tiêu app.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Plasma Volume Deficit, Cardiac Drift (+3-5 bpm) &amp; Core Thermoregulation</t>
+          <t>Hydration during activity (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1128,17 +1155,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>What Is a Normal Testosterone Level?</t>
+          <t>Understanding low testosterone testing</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Testosterone bao nhiêu là bình thường?</t>
+          <t>Testosterone thấp: chẩn đoán cần hơn một con số</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Biến thiên theo tuổi, giờ đo, chỉ định xét nghiệm</t>
+          <t>Nồng độ testosterone thay đổi theo thời điểm, tình trạng sức khỏe và phương pháp xét nghiệm.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -1158,12 +1185,12 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXH_01)</t>
+          <t>Revised — MW_SXH_01; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1173,22 +1200,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Nồng Độ Testosterone Chuẩn Là Bao Nhiêu? Hiểu Về Dao Động Sinh Học 24 Giờ &amp; Chỉ Số Free T</t>
+          <t>Testosterone thấp: chẩn đoán cần hơn một con số</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>What Is a Normal Testosterone Level? Circadian Rhythms, Free T vs. Total T &amp; Age Curves</t>
+          <t>Understanding low testosterone testing</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Khoảng tham chiếu chuẩn của Testosterone toàn phần ở nam giới khỏe mạnh là 300–1.000 ng/dL, nhưng bắt buộc phải lấy máu trước 10:00 sáng. Đừng chỉ nhìn vào Total T; chỉ số Free T (dao động 9–30 pg/mL hoặc 1.5%–2% tổng lượng) mới là thước đo phản ánh chính xác tình trạng sinh lực và chuyển hóa.</t>
+          <t>Nếu có triệu chứng kéo dài, ghi thuốc, giấc ngủ, bệnh gần đây và mong muốn có con để trao đổi khi khám. Hỏi kết quả cần lặp lại hay đánh giá thêm gì, thay vì chỉ so với một ngưỡng trên mạng.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Circadian Diurnal Testosterone Curve, Free vs Total T &amp; SHBG</t>
+          <t>Understanding low testosterone testing (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1205,17 +1232,17 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Erectile Dysfunction: What Your Body May Be Telling You</t>
+          <t>Erectile dysfunction and whole-person assessment</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Rối loạn cương có thể phản ánh điều gì?</t>
+          <t>Rối loạn cương: dấu hiệu nên được đánh giá toàn diện</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Yếu tố mạch máu, chuyển hóa, tâm lý</t>
+          <t>Khó đạt hoặc duy trì cương có thể liên quan mạch máu, thần kinh, thuốc, hormone và yếu tố tâm lý.</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -1230,17 +1257,17 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/16530932/</t>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXH_02)</t>
+          <t>Revised — MW_SXH_02; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1250,22 +1277,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Rối Loạn Cương Dương (ED): Tín Hiệu Báo Động Sớm Của Hệ Tuần Hoàn &amp; Sức Khỏe Chuyển Hóa</t>
+          <t>Rối loạn cương: dấu hiệu nên được đánh giá toàn diện</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Erectile Dysfunction Decoded: The Early Cardiovascular &amp; Metabolic Warning System</t>
+          <t>Erectile dysfunction and whole-person assessment</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Đừng xem rối loạn cương chỉ là chuyện phòng the; hãy xem nó là bài kiểm tra sức khỏe động mạch. Động mạch hang nhỏ hơn nhiều so với động mạch vành tim. Khám tim mạch, xét nghiệm mỡ máu, kiểm tra đường huyết và phục hồi độ đàn hồi nội mô là bước đi sống còn hàng đầu.</t>
+          <t>Ghi thời điểm bắt đầu, hoàn cảnh, thuốc và triệu chứng khác. Trao đổi với bác sĩ về sức khỏe tim mạch, chuyển hóa và lựa chọn điều trị. Vận động, ngừng hút thuốc và chăm sóc giấc ngủ có thể là một phần kế hoạch.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Endothelial Health, Arterial Compliance &amp; Resting Heart Rate</t>
+          <t>Erectile dysfunction and whole-person assessment (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1282,17 +1309,17 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Does Poor Sleep Affect Testosterone?</t>
+          <t>Sleep restriction and testosterone: interpreting the evidence</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Thiếu ngủ ảnh hưởng testosterone?</t>
+          <t>Thiếu ngủ và testosterone: không quy đổi thành số năm già đi</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Giấc ngủ và chức năng nội tiết</t>
+          <t>Một nghiên cứu nhỏ ở nam trẻ ghi nhận thay đổi testosterone sau hạn chế ngủ.</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1312,12 +1339,12 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J12" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXH_03)</t>
+          <t>Revised — MW_SXH_03; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1327,22 +1354,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Giấc Ngủ &amp; Hormone Nam: Vì Sao Mất 1 Tuần Ngủ Thiếu Khiến Testosterone Tụt Dốc Như Già Đi 10 Tuổi?</t>
+          <t>Thiếu ngủ và testosterone: không quy đổi thành số năm già đi</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Sleep Deprivation &amp; Testosterone: Why One Week of Sleep Loss Ages Your Hormones by a Decade</t>
+          <t>Sleep restriction and testosterone: interpreting the evidence</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Phần lớn testosterone được sản xuất và đồng hóa trong các chu kỳ ngủ sâu và ngủ REM. Thiếu ngủ mãn tính kích hoạt trục stress HPA, đẩy cortisol tăng cao và bóp nghẹt quá trình phục hồi của tinh hoàn. Ngủ đủ 7–8.5 tiếng với giờ giấc nhất quán là liều 'thuốc tăng test' tự nhiên mạnh mẽ nhất.</t>
+          <t>Ưu tiên cơ hội ngủ đủ và lịch ổn định. Nếu mệt hoặc giảm ham muốn, xem cả giấc ngủ, stress, thuốc và bệnh nền. Triệu chứng kéo dài cần đánh giá riêng thay vì suy nồng độ từ số giờ ngủ.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Deep Sleep Duration, REM Fragmentation &amp; Sleep Debt</t>
+          <t>Sleep restriction and testosterone: interpreting the evidence (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1359,17 +1386,17 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Stress and Male Sexual Performance</t>
+          <t>Stress and male sexual function</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Stress và chức năng tình dục nam</t>
+          <t>Stress và chức năng tình dục nam: tránh tự chẩn đoán cortisol</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Lo âu hiệu suất và đáp ứng tình dục</t>
+          <t>Stress và lo âu có thể góp phần làm giảm ham muốn hoặc khó cương, nhưng chúng chỉ là một phần bức tranh.</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -1384,17 +1411,17 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20358897/</t>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXH_04)</t>
+          <t>Revised — MW_SXH_04; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1404,22 +1431,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Stress &amp; Phong Độ Phòng The: Trục HPA, Độc Tính Cortisol &amp; Phản Ứng Ức Chế Thần Kinh</t>
+          <t>Stress và chức năng tình dục nam: tránh tự chẩn đoán cortisol</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Stress and Male Sexual Performance: The HPA Axis, Cortisol Surge &amp; Autonomic Interference</t>
+          <t>Stress and male sexual function</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Cơ chế cương cứng là hiện tượng hoàn toàn phụ thuộc vào hệ thần kinh phó giao cảm (Parasympathetic). Bạn không thể cương cứng khi cơ thể đang ở trạng thái chiến đấu (Fight or Flight). Làm chủ các kỹ thuật kích hoạt dây thần kinh phế vị và hạ thấp cortisol là chìa khóa mở khóa bản lĩnh.</t>
+          <t>Xem tình huống nào làm tăng áp lực và trao đổi về nhịp độ thoải mái với bạn tình. Chăm sóc ngủ, nghỉ và hoạt động đều. Nếu triệu chứng kéo dài, đưa cả danh sách thuốc và bệnh nền vào buổi tư vấn.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Stress Score, Sympathetic Overdrive &amp; Cortisol/Testosterone Ratio</t>
+          <t>Stress and male sexual function (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1436,17 +1463,17 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Morning Erections: What Is Normal?</t>
+          <t>Morning erections and what they mean</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Cương buổi sáng thế nào là bình thường?</t>
+          <t>Cương buổi sáng: một dấu hiệu, không phải bài kiểm tra hormone</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Cơ chế sinh lý và dấu hiệu cần khám</t>
+          <t>Cương khi ngủ hoặc thức dậy có thể xảy ra bình thường và thay đổi theo giấc ngủ, thuốc, tuổi cùng sức khỏe.</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1461,17 +1488,17 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/12495694/</t>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXH_05)</t>
+          <t>Revised — MW_SXH_05; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1481,22 +1508,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Hiện Tượng Cương Buổi Sáng (NPT): Dấu Ấn Sinh Học Của Chu Kỳ Giấc Ngủ REM &amp; Sức Khỏe Mạch Máu</t>
+          <t>Cương buổi sáng: một dấu hiệu, không phải bài kiểm tra hormone</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Nocturnal Penile Tumescence (NPT): The Biological Signature of REM Sleep &amp; Vascular Integrity</t>
+          <t>Morning erections and what they mean</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Cương buổi sáng là sự phản chiếu của chu kỳ ngủ REM cuối cùng trước khi thức giấc. Ở nam giới khỏe mạnh, có 3–5 đợt cương tự nhiên kéo dài 25–35 phút mỗi đêm nhằm cung cấp oxy bảo vệ mô thể hang không bị xơ hóa. Sự biến mất liên tục của cương buổi sáng là tín hiệu cảnh báo sớm bệnh mạch máu hoặc thiếu hụt testosterone.</t>
+          <t>Nếu lo ngại, xem thay đổi có kéo dài và đi cùng khó cương trong tình huống khác, đau hay giảm ham muốn không. Ghi thuốc và lịch ngủ để trao đổi khi khám, thay vì tự kiểm tra liên tục mỗi sáng.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>REM Sleep Episodes, Sympathetic Inhibition &amp; Morning Erections (NPT)</t>
+          <t>Morning erections and what they mean (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1513,17 +1540,17 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>How Exercise Supports Sexual Health</t>
+          <t>Physical activity and erectile health</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Vận động hỗ trợ sức khỏe tình dục</t>
+          <t>Vận động và chức năng cương: hỗ trợ sức khỏe chung</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Tim mạch, thể lực và chức năng tình dục</t>
+          <t>Vận động là một phần chăm sóc tim mạch và có thể nằm trong kế hoạch điều trị rối loạn cương.</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -1538,17 +1565,17 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/21883955/</t>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/treatment</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXH_06)</t>
+          <t>Revised — MW_SXH_06; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1558,22 +1585,22 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Vận Động Thể Thao Tăng Cường Bản Lĩnh: Cardio Zone 2, Sức Mạnh Khung Chậu &amp; Lưu Lượng Máu</t>
+          <t>Vận động và chức năng cương: hỗ trợ sức khỏe chung</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Exercise as Sexual Medicine: Zone 2 Cardio, Pelvic Circulation &amp; Endothelial Health</t>
+          <t>Physical activity and erectile health</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Vận động thể thao tác động lên bản lĩnh phái mạnh qua hai mũi nhọn: Cardio Zone 2 nâng cao VO2 Max và kích thích sản sinh Nitric Oxide khắp hệ mạch máu; trong khi tập luyện cơ sàn chậu (Pelvic Floor) củng cố van khóa tĩnh mạch để duy trì độ cứng hoàn hảo cấp độ 4.</t>
+          <t>Chọn hoạt động có thể duy trì và tăng từ từ. Nếu có rối loạn cương, kết hợp đánh giá bệnh nền, thuốc, tâm lý và các lựa chọn điều trị thay vì chỉ tăng số buổi tập.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Cardio Fitness (VO2 Max), Endothelial eNOS &amp; Pelvic Floor Strength</t>
+          <t>Physical activity and erectile health (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1590,17 +1617,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Male Fertility: What Affects Sperm Quality?</t>
+          <t>Male fertility: health, medicines and assessment</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yếu tố ảnh hưởng chất lượng tinh trùng</t>
+          <t>Sinh sản nam: chú ý sức khỏe, thuốc và đánh giá phù hợp</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Lối sống, sức khỏe và fertility</t>
+          <t>Khả năng sinh sản nam phụ thuộc nhiều yếu tố và không thể biết chỉ từ lượng tinh dịch nhìn thấy hoặc mức ham muốn.</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -1615,17 +1642,17 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/20308044/</t>
+          <t>https://integration.asrm.org/practice-guidance/practice-committee-documents/diagnosis-and-treatment-of-infertility-in-men-aua-asrm-guideline-part2/</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXH_07)</t>
+          <t>Revised — MW_SXH_07; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1635,22 +1662,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Bản Đồ Sinh Sản Nam Giới: Nhiệt Độ Bìu, Ô Nhiễm Môi Trường, Vi Chất &amp; Chu Kỳ Sinh Tinh</t>
+          <t>Sinh sản nam: chú ý sức khỏe, thuốc và đánh giá phù hợp</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The Male Fertility Blueprint: Scrotal Thermoregulation, Toxins &amp; The 74-Day Cycle</t>
+          <t>Male fertility: health, medicines and assessment</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Nhiệt độ bìu bắt buộc phải duy trì ở mức 33°C–34.5°C. Thói quen tắm nước nóng, ngâm bồn, ngồi lái xe nhiều giờ liên tục hoặc để laptop lên đùi làm nhiệt độ tinh hoàn tăng vọt, gây chết tế bào mầm hàng loạt. Bảo vệ khả năng sinh sản đòi hỏi giải nhiệt vùng kín, loại bỏ đồ nhựa chứa phthalates/BPA và thanh lọc lối sống trong tối thiểu 3 tháng.</t>
+          <t>Khi mong có con, nói rõ mọi thuốc, testosterone, steroid và chất bổ sung đang dùng. Nếu cần, bác sĩ sẽ hướng dẫn xét nghiệm tinh dịch và diễn giải trong bối cảnh cả hai người; không tự ngừng thuốc điều trị.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Scrotal Thermoregulation, Endocrine Disruptors (EDCs) &amp; Oxidative Stress</t>
+          <t>Male fertility: health, medicines and assessment (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1667,17 +1694,17 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>When Should Men Get Their Hormones Checked?</t>
+          <t>When testosterone testing is appropriate</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Khi nào nam giới cần xét nghiệm hormone?</t>
+          <t>Khi nào nên xét nghiệm testosterone?</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Triệu chứng, xét nghiệm, tránh tự điều trị</t>
+          <t>Hướng dẫn không khuyến nghị sàng lọc đại trà testosterone ở người không triệu chứng.</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -1697,12 +1724,12 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXH_08)</t>
+          <t>Revised — MW_SXH_08; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1712,22 +1739,22 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Khi Nào Nam Giới Cần Kiểm Tra Hormone? Hướng Dẫn Đọc Bảng Xét Nghiệm Chuẩn Y Khoa</t>
+          <t>Khi nào nên xét nghiệm testosterone?</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>When to Test Your Hormones: Clinical Guidelines for Total T, Free T, SHBG, LH &amp; Prolactin</t>
+          <t>When testosterone testing is appropriate</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Chỉ xét nghiệm hormone khi có các triệu chứng lâm sàng rõ rệt (mất ham muốn, mất cương buổi sáng, teo cơ, mệt mỏi mạn tính). Bắt buộc phải lấy máu lúc đói trước 10:00 sáng. Bảng xét nghiệm chuẩn phải bao gồm: Total T, Free T (hoặc tính qua SHBG + Albumin), LH, FSH, Prolactin và Estradiol nhạy cảm.</t>
+          <t>Trao đổi triệu chứng cụ thể, thời điểm khởi phát, thuốc và bệnh gần đây. Nếu được chỉ định, hỏi cách chuẩn bị, thời gian lấy máu và kế hoạch lặp lại; báo mong muốn có con trước khi cân nhắc điều trị.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Diurnal Blood Sampling, Total/Free T, SHBG, LH &amp; Prolactin Differential</t>
+          <t>When testosterone testing is appropriate (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1771,17 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Why Communication Matters More Than You Think</t>
+          <t>Practical communication in a relationship</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Vì sao giao tiếp quan trọng trong quan hệ?</t>
+          <t>Giao tiếp cặp đôi: bắt đầu từ một cuộc trò chuyện cụ thể</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Giao tiếp và hài lòng mối quan hệ</t>
+          <t>Giao tiếp hữu ích gồm nói rõ trải nghiệm, lắng nghe và tôn trọng ranh giới.</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -1769,17 +1796,17 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC9153093/</t>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J18" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_REL_01)</t>
+          <t>Revised — MW_REL_01; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1789,22 +1816,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Nghệ Thuật Giao Tiếp Cặp Đôi: Giải Mã Tỷ Lệ Vàng 5:1 &amp; Cơ Chế An Toàn Sinh Học Thần Kinh</t>
+          <t>Giao tiếp cặp đôi: bắt đầu từ một cuộc trò chuyện cụ thể</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Couple Communication Science: The 5:1 Gottman Ratio &amp; Neurobiological Safety</t>
+          <t>Practical communication in a relationship</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Trong một mối quan hệ bền vững, cần tối thiểu 5 tương tác tích cực (lắng nghe, khen ngợi, chạm nhẹ, đùa vui) để hóa giải 1 tương tác tiêu cực (chỉ trích, phòng thủ). Khi nhịp tim của một trong hai người vượt quá 100 bpm trong lúc tranh cãi, não bộ rơi vào trạng thái tê liệt cảm xúc—hãy tạm dừng 20 phút trước khi tiếp tục.</t>
+          <t>Gợi ý thực hành: chọn một việc cụ thể, nói “Tôi thấy… và tôi mong…” rồi hỏi đối phương hiểu thế nào. Đổi lượt nói và cùng thống nhất một việc nhỏ có thể thử trong tuần, thay vì giải quyết mọi bất đồng cùng lúc.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Autonomic Safety, Polyvagal Tone &amp; Gottman 5:1 Ratio</t>
+          <t>Practical communication in a relationship (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1821,17 +1848,17 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>How to Talk About Sex With Your Partner</t>
+          <t>Talking about sex, preferences and boundaries</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Cách trao đổi chuyện tình dục với bạn đời</t>
+          <t>Mở lời về tình dục: mong muốn, ranh giới và sự đồng thuận</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Nhu cầu, kỳ vọng, ranh giới</t>
+          <t>Nghiên cứu tổng hợp ghi nhận giao tiếp tình dục tốt hơn có liên hệ với chức năng tình dục, nhưng chưa chứng minh một cuộc nói chuyện sẽ chữa mọi khó khăn.</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -1846,17 +1873,17 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC6699928/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30777780/</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_REL_02)</t>
+          <t>Revised — MW_REL_02; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1866,22 +1893,22 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cách Mở Lời Về Chuyện Tình Dục: Xây Dựng Không Gian An Toàn Cho Mong Muốn &amp; Ranh Giới</t>
+          <t>Mở lời về tình dục: mong muốn, ranh giới và sự đồng thuận</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Talking About Sex With Your Partner: Creating Emotional Safety for Desires &amp; Boundaries</t>
+          <t>Talking about sex, preferences and boundaries</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Đừng bao giờ bắt đầu một cuộc đối thoại nhạy cảm về tình dục ngay trên giường hoặc ngay sau một trải nghiệm không như ý. Hãy chọn một thời điểm trung tính khi cả hai đều thư giãn và mặc quần áo đầy đủ, bắt đầu bằng lời khẳng định tình yêu và tập trung vào những điều bạn mong muốn trải nghiệm thêm.</t>
+          <t>Chọn lúc riêng tư ngoài thời điểm đang quan hệ. Có thể hỏi “Điều gì làm bạn thoải mái?” và nêu rõ điều mình muốn hoặc không muốn. Nghe câu trả lời mà không thương lượng để vượt qua một lời từ chối.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Vulnerability, Psychological Safety &amp; Sexual Attunement</t>
+          <t>Talking about sex, preferences and boundaries (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1898,17 +1925,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Emotional Intimacy: Beyond Physical Attraction</t>
+          <t>Building emotional intimacy</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Gắn kết cảm xúc ngoài hấp dẫn thể chất</t>
+          <t>Thân mật cảm xúc: xây từ sự quan tâm hằng ngày</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Sự thân mật và thấu hiểu</t>
+          <t>Thân mật cảm xúc có thể phát triển khi hai người cảm thấy được lắng nghe và tôn trọng.</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -1923,17 +1950,17 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/18652807/</t>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_REL_03)</t>
+          <t>Revised — MW_REL_03; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1943,22 +1970,22 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sự Thân Mật Cảm Xúc: Nền Móng Oxytocin Vượt Ra Ngoài Sự Cuốn Hút Thể Xác Thuần Túy</t>
+          <t>Thân mật cảm xúc: xây từ sự quan tâm hằng ngày</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Emotional Intimacy: The Neurochemistry of Oxytocin &amp; Long-Term Attachment Bonding</t>
+          <t>Building emotional intimacy</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Sức hấp dẫn thể xác sẽ tự nhiên suy giảm sau 18–24 tháng do hiện tượng dung nạp dopamine. Sự thân mật cảm xúc được xây dựng qua những khoảnh khắc bộc lộ sự yếu đuối, lắng nghe không phán xét và những cái ôm 20 giây giúp kích hoạt oxytocin, biến tình yêu từ một cơn sốt thành một bến đỗ bình yên trọn đời.</t>
+          <t>Gợi ý thực hành: hỏi một điều đối phương muốn chia sẻ trong ngày và nghe trước khi đưa lời khuyên. Thống nhất hình thức gần gũi cả hai thích, có thể là đi bộ, trò chuyện hoặc thời gian riêng, không bắt buộc tiếp xúc cơ thể.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Oxytocin Signaling, Ventral Striatum Activation &amp; Vagal Attunement</t>
+          <t>Building emotional intimacy (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -1975,17 +2002,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>How Stress Affects Your Relationship</t>
+          <t>When stress affects a relationship</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Stress ảnh hưởng mối quan hệ ra sao?</t>
+          <t>Khi stress lan vào mối quan hệ: nói rõ nhu cầu hỗ trợ</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Căng thẳng và tương tác cặp đôi</t>
+          <t>Áp lực công việc hoặc đời sống có thể làm một người ít kiên nhẫn hay thu mình, từ đó ảnh hưởng tương tác.</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -2000,17 +2027,17 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/17588698/</t>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J21" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_REL_04)</t>
+          <t>Revised — MW_REL_04; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2020,22 +2047,22 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Hiệu Ứng Lây Lan Căng Thẳng: Bảo Vệ Mối Quan Hệ Khỏi Sự Cạn Kiệt Năng Lượng Thần Kinh</t>
+          <t>Khi stress lan vào mối quan hệ: nói rõ nhu cầu hỗ trợ</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Stress Spillover in Relationships: Shielding Intimacy from Autonomic Burnout</t>
+          <t>When stress affects a relationship</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Bộ não không thể phân biệt giữa áp lực hạn chót công việc với mối đe dọa sinh tử. Khi cạn kiệt tài nguyên nhận thức, khả năng kiềm chế của thùy trán bị tê liệt. Hãy thiết lập một 'nghi thức chuyển tiếp' 15 phút (nghe nhạc, tắm nước ấm, thở chậm) để xả hết cortisol trước khi tương tác với gia đình.</t>
+          <t>Gợi ý thực hành: khi căng, nói bạn cần được nghe, hỗ trợ việc cụ thể hay có thời gian yên tĩnh. Chọn lúc quay lại trao đổi để khoảng nghỉ không trở thành bỏ mặc. Cả hai đều có thể đặt giới hạn hỗ trợ.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Stress Spillover, Window of Tolerance &amp; Autonomic Burnout</t>
+          <t>When stress affects a relationship (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2052,17 +2079,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Healthy Conflict: How Couples Disagree Better</t>
+          <t>Managing disagreements with less harm</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Bất đồng lành mạnh trong mối quan hệ</t>
+          <t>Tranh luận ít gây tổn thương hơn: tạm dừng và quay lại vấn đề</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Xung đột và giải quyết xung đột</t>
+          <t>Bất đồng là điều có thể xảy ra trong quan hệ.</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -2077,17 +2104,17 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/6620126/</t>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J22" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_REL_05)</t>
+          <t>Revised — MW_REL_05; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2097,22 +2124,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Xung Đột Lành Mạnh: Chuyển Hóa Tranh Cãi Thành Sự Thấu Hiểu Bằng Kỹ Thuật Tự Hạ Hỏa Thần Kinh</t>
+          <t>Tranh luận ít gây tổn thương hơn: tạm dừng và quay lại vấn đề</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Healthy Conflict Mastery: Diffusing Marital Arguments Through Autonomic Self-Soothing</t>
+          <t>Managing disagreements with less harm</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Khi tranh cãi đẩy nhịp tim vượt quá 100 bpm, não bộ rơi vào trạng thái 'điếc sinh lý'—bạn không còn khả năng tiếp thu bất kỳ lập luận logic nào của đối phương. Hãy áp dụng quy tắc tạm dừng bắt buộc 20 phút để hệ thần kinh tự xoa dịu bằng cách đi dạo hoặc hít thở sâu, sau đó sử dụng các 'tín hiệu sửa chữa' (Repair Attempts) để tái thiết lập kết nối.</t>
+          <t>Gợi ý thực hành: thống nhất tín hiệu xin nghỉ, thời điểm quay lại và chỉ bàn một vấn đề cụ thể. Khi trở lại, mô tả sự việc và điều mình cần thay vì công kích con người; kiểm tra xem đã hiểu đúng đối phương chưa.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Autonomic Flooding (&gt;100 bpm), Physiological Timeout &amp; Repair Attempts</t>
+          <t>Managing disagreements with less harm (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2129,17 +2156,17 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Why Partners Sometimes Want Sex at Different Frequencies</t>
+          <t>When partners want different amounts of sex</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Vì sao hai người có mức ham muốn khác nhau?</t>
+          <t>Khi hai người có mức ham muốn khác nhau</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Desire discrepancy và giao tiếp</t>
+          <t>Khác biệt ham muốn không tự có nghĩa một người bị bệnh hoặc không còn yêu.</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -2154,17 +2181,17 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/11454441/</t>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_REL_06)</t>
+          <t>Revised — MW_REL_06; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2174,22 +2201,22 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Hóa Giải Sự Lệch Pha Ham Muốn: Hiểu Về Ham Muốn Tự Phát (Spontaneous) So Với Đáp Ứng (Responsive)</t>
+          <t>Khi hai người có mức ham muốn khác nhau</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Bridging Desire Discrepancy: Spontaneous vs. Responsive Desire in Long-Term Partnerships</t>
+          <t>When partners want different amounts of sex</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Có hai cơ chế ham muốn sinh học: Ham muốn Tự phát (Spontaneous - bỗng dưng thèm muốn từ hư không, phổ biến ở nam giới) và Ham muốn Đáp ứng (Responsive - chỉ xuất hiện sau khi có sự kích thích thể chất và bối cảnh thư giãn an toàn, gặp ở đa số phụ nữ và nhiều nam giới). Hiểu rằng 'sự sẵn lòng thử' (Willingness) khác với 'sự thèm khát sẵn' là chìa khóa phá vỡ vòng lặp bế tắc.</t>
+          <t>Trao đổi khi cả hai bình tĩnh về điều thấy thoải mái, áp lực và hình thức thân mật mong muốn. Có thể dành thời gian gần gũi mà không cam kết phải quan hệ; bất kỳ ai cũng được đổi ý hoặc dừng lại.</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Spontaneous vs Responsive Desire, Basson Model &amp; Erotic Context</t>
+          <t>When partners want different amounts of sex (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2206,17 +2233,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Building Trust in Long-Term Relationships</t>
+          <t>Trust through observable actions</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Xây dựng lòng tin lâu dài</t>
+          <t>Lòng tin: bắt đầu bằng hành vi có thể quan sát</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Nhất quán, trung thực và hỗ trợ</t>
+          <t>Lòng tin gắn với trải nghiệm được tôn trọng, sự nhất quán và ranh giới.</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -2231,17 +2258,17 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/18652807/</t>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_REL_07)</t>
+          <t>Revised — MW_REL_07; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2251,22 +2278,22 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Khoa Học Về Lòng Tin: Tính Nhất Quán Nhỏ Hàng Ngày Tạo Nên Sự Vững Chãi Tâm Lý Dài Hạn</t>
+          <t>Lòng tin: bắt đầu bằng hành vi có thể quan sát</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>The Architecture of Trust: Micro-Attunements, Reliability &amp; Emotional Vulnerability</t>
+          <t>Trust through observable actions</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Lòng tin được định nghĩa bằng phương trình toán học tâm lý: Khả năng hy sinh lợi ích ngắn hạn của bản thân để bảo vệ hạnh phúc của đối tác. Xây dựng lòng tin đòi hỏi sự nhất quán tuyệt đối giữa lời nói và hành động, phản hồi tích cực trước các 'lời mời kết nối' (Bids for Connection) và tạo ra một vùng đệm an toàn không phán xét.</t>
+          <t>Gợi ý thực hành: chọn một cam kết nhỏ, rõ và khả thi; nếu không làm được, báo sớm và bàn cách sửa. Trao đổi điều gì làm mỗi người thấy an toàn mà vẫn tôn trọng sự riêng tư, không đòi quyền kiểm soát.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Adult Attachment Stability, Neurobiological Safety &amp; Micro-Attunements</t>
+          <t>Trust through observable actions (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2283,17 +2310,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Can Better Sleep Improve Your Relationship?</t>
+          <t>Sleep and relationships</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Ngủ tốt có cải thiện mối quan hệ?</t>
+          <t>Giấc ngủ và mối quan hệ: cùng tìm cách nghỉ phù hợp</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Ngủ, điều tiết cảm xúc và tương tác</t>
+          <t>Nghiên cứu tổng hợp ghi nhận liên hệ giữa chất lượng giấc ngủ và quan hệ.</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
@@ -2308,17 +2335,17 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/24838689/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39514915/</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J25" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_REL_08)</t>
+          <t>Revised — MW_REL_08; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2328,22 +2355,22 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Giấc Ngủ &amp; Hạnh Phúc Lứa Đôi: Thiếu Ngủ Làm Giảm Sự Thấu Cảm &amp; Tăng Xung Đột Thế Nào?</t>
+          <t>Giấc ngủ và mối quan hệ: cùng tìm cách nghỉ phù hợp</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Sleep and Relationship Health: How Sleep Debt Blunts Empathy &amp; Escalates Spousal Conflict</t>
+          <t>Sleep and relationships</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Mất ngủ làm tổn thương trực tiếp mạch thần kinh thùy trán - hạch hạnh nhân, khiến con người mất khả năng giải mã chính xác biểu cảm gương mặt của bạn đời (dễ nhìn nhận một khuôn mặt trung tính thành đe dọa hoặc thù địch). Ngủ chung giường nhưng tối ưu hóa nhiệt độ, nệm độc lập hoặc áp dụng 'ly hôn giấc ngủ' (Sleep Divorce) khi một người ngáy ngủ là giải pháp y khoa bảo vệ hạnh phúc hôn nhân.</t>
+          <t>Gợi ý thực hành: bàn giờ ngủ, tiếng ồn, ánh sáng và phân chia việc chăm sóc để mỗi người có cơ hội nghỉ. Chọn thời điểm tỉnh táo cho cuộc nói chuyện khó. Các cách ngủ khác nhau có thể phù hợp nếu cả hai đồng thuận.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sleep Debt Spillover, Empathy Circuitry &amp; Conflict Escalation</t>
+          <t>Sleep and relationships (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2360,17 +2387,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>The Science of Male Sexual Desire</t>
+          <t>Male sexual desire beyond testosterone</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Khoa học về ham muốn tình dục nam</t>
+          <t>Ham muốn nam giới: không chỉ là testosterone</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Sinh học, tâm lý, bối cảnh</t>
+          <t>Ham muốn chịu ảnh hưởng của sức khỏe, thuốc, tâm trạng, bối cảnh và mối quan hệ.</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -2385,17 +2412,17 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/17397950/</t>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J26" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXO_01)</t>
+          <t>Revised — MW_SXO_01; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2405,22 +2432,22 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Khoa Học Ham Muốn Nam Giới: Trục Thần Kinh - Nội Tiết, Dopamine &amp; Động Lực Sinh Học</t>
+          <t>Ham muốn nam giới: không chỉ là testosterone</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>The Science of Male Sexual Desire: The Neuroendocrine Axis, Dopamine &amp; Drive</t>
+          <t>Male sexual desire beyond testosterone</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Testosterone tạo ra độ nhạy cảm của các thụ thể thần kinh, nhưng Dopamine mới là chất tạo ra động lực khao khát. Khi bạn mệt mỏi, thiếu ngủ, lạm dụng chất kích thích hoặc đối mặt với sự nhàm chán, dopamine bị suy kiệt khiến ham muốn tình dục biến mất dù nồng độ testosterone trong máu hoàn toàn bình thường.</t>
+          <t>Khi thay đổi gây khó chịu, ghi thời điểm, tình huống và triệu chứng đi kèm. Trao đổi không phán xét với bạn tình; kiểm tra cả mệt mỏi, đau, stress và thuốc trong tư vấn.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Mesolimbic Dopamine Circuit, Hypothalamic MPOA &amp; Androgen Priming</t>
+          <t>Male sexual desire beyond testosterone (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2437,17 +2464,17 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>What Happens During Male Sexual Arousal?</t>
+          <t>Arousal, erections and consent</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Điều gì xảy ra khi nam giới hưng phấn?</t>
+          <t>Hưng phấn và cương: phản ứng cơ thể không thay cho đồng thuận</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Hệ thần kinh, tuần hoàn, đáp ứng tình dục</t>
+          <t>Cương là phản ứng phối hợp mạch máu và thần kinh, chịu ảnh hưởng cả yếu tố thể chất và tâm lý.</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -2462,17 +2489,17 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/10853004/</t>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXO_02)</t>
+          <t>Revised — MW_SXO_02; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2482,22 +2509,22 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sinh Lý Học Của Sự Hưng Phấn: Dòng Thác Thần Kinh - Mạch Máu Từ Não Bộ Đến Thể Hang</t>
+          <t>Hưng phấn và cương: phản ứng cơ thể không thay cho đồng thuận</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>What Happens During Male Sexual Arousal? The Neurovascular Cascade from Cortex to Corpora</t>
+          <t>Arousal, erections and consent</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Cương cứng là sự thư giãn của cơ trơn thể hang để dòng máu lấp đầy các khoang xốp. Bất kỳ yếu tố nào làm co thắt mạch (nicotine, căng thẳng, mỡ máu cao) đều chặn đứng quá trình này. Cơ chế duy trì độ cứng vững chắc dựa vào hiện tượng chèn ép tĩnh mạch tự nhiên khi áp lực thể hang đạt 100 mmHg.</t>
+          <t>Ưu tiên trao đổi rõ sự thoải mái và đồng thuận thay vì đánh giá phản ứng như một bài kiểm tra. Nếu khó cương lặp lại, ghi hoàn cảnh, thuốc và triệu chứng để trao đổi với bác sĩ.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Pelvic Splanchnic Nerve Discharge, NO/cGMP Cascade &amp; Venous Occlusion</t>
+          <t>Arousal, erections and consent (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2514,17 +2541,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Libido vs. Testosterone: What’s the Difference?</t>
+          <t>Does low desire always mean low testosterone?</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Ham muốn và testosterone khác gì nhau?</t>
+          <t>Ham muốn thấp có luôn là testosterone thấp?</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Testosterone không quyết định hoàn toàn ham muốn</t>
+          <t>Nhiều người có ham muốn thay đổi trong khi testosterone không thiếu; ngược lại, chẩn đoán thiếu hormone cần cả triệu chứng và kết quả xét nghiệm phù hợp.</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -2539,17 +2566,17 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/24024838/</t>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J28" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXO_03)</t>
+          <t>Revised — MW_SXO_03; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2559,22 +2586,22 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ham Muốn Tình Dục &amp; Testosterone: Điểm Khác Biệt Giữa Nhiên Liệu Sinh Học &amp; Tâm Lý Học</t>
+          <t>Ham muốn thấp có luôn là testosterone thấp?</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Libido vs. Testosterone: Disentangling Biological Fuel from Psychosocial Catalysts</t>
+          <t>Does low desire always mean low testosterone?</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Testosterone giống như dầu nhớt trong động cơ xe: Thiếu nhớt xe sẽ không chạy, nhưng đổ ngập nhớt không làm xe chạy nhanh hơn. Ngưỡng bão hòa của ham muốn thường rơi vào khoảng 300–350 ng/dL. Nếu bạn đã có mức T bình thường mà vẫn mất ham muốn, hãy tìm kiếm nguyên nhân ở giấc ngủ, stress, trầm cảm hoặc chất lượng mối quan hệ.</t>
+          <t>Xác định thay đổi nào gây khó chịu và điều gì xảy ra cùng thời điểm. Nếu cần đánh giá, hỏi về xét nghiệm buổi sáng lặp lại và các nguyên nhân khác. Nói rõ kế hoạch có con trước khi thảo luận điều trị.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Androgen Threshold Model, Receptor Sensitivity &amp; Central Dopamine</t>
+          <t>Does low desire always mean low testosterone? (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2591,17 +2618,17 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Is There Such a Thing as a Normal Sex Drive?</t>
+          <t>Is there a normal amount of sexual desire?</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Có mức ham muốn tình dục bình thường không?</t>
+          <t>Có mức ham muốn bình thường cho tất cả không?</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Biến thiên cá nhân và bối cảnh</t>
+          <t>Tần suất mong muốn tình dục rất khác nhau.</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -2616,17 +2643,17 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/10704733/</t>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXO_04)</t>
+          <t>Revised — MW_SXO_04; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2636,22 +2663,22 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Có Mức Ham Muốn Chuẩn Không? Mô Hình Hai Cơ Chế Kiểm Soát (Dual Control) &amp; Tính Đa Dạng</t>
+          <t>Có mức ham muốn bình thường cho tất cả không?</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Is There a Normal Sex Drive? The Dual Control Model of Sexual Excitation and Inhibition</t>
+          <t>Is there a normal amount of sexual desire?</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Ham muốn tình dục không phải là một con số cố định mà là một phổ sinh học linh hoạt. Phản ứng tình dục được điều khiển bởi hai cơ chế độc lập: Hệ Thống Kích Thích (SES - Chân Ga) và Hệ Thống Ức Chế (SIS - Chân Phanh). Thay vì cố gắng 'đạp thêm ga', bí quyết khơi dậy ham muốn thường nằm ở việc nhận diện và 'nhả chân phanh' (lo âu, mệt mỏi, bất an).</t>
+          <t>Gợi ý thực hành: mô tả điều mình thấy phù hợp và hỏi mong muốn của đối phương mà không đặt mức tối thiểu. Cùng thỏa thuận hình thức thân mật và quyền dừng, không dùng lịch như nghĩa vụ.</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Dual Control Model (SIS/SES), Contextual Arousal &amp; Libido Diversity</t>
+          <t>Is there a normal amount of sexual desire? (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2695,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>The Science of Orgasms and Ejaculation</t>
+          <t>Orgasm and ejaculation: related but distinct</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Khoa học về cực khoái và xuất tinh</t>
+          <t>Cực khoái và xuất tinh: có liên quan nhưng không hoàn toàn giống nhau</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Khác biệt sinh lý giữa cực khoái và xuất tinh</t>
+          <t>Cực khoái là trải nghiệm cảm giác, còn xuất tinh là quá trình tống tinh dịch; chúng thường đi cùng nhưng có thể tách biệt.</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -2693,17 +2720,17 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/12470685/</t>
+          <t>https://www.nhs.uk/conditions/ejaculation-problems/</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXO_05)</t>
+          <t>Revised — MW_SXO_05; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2713,22 +2740,22 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Khoa Học Cực Khoái &amp; Xuất Tinh: Hai Cơ Chế Thần Kinh Riêng Biệt &amp; Thời Kỳ Trơ Sinh Lý</t>
+          <t>Cực khoái và xuất tinh: có liên quan nhưng không hoàn toàn giống nhau</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>The Neurobiology of Orgasm and Ejaculation: Divergent Pathways &amp; The Refractory Period</t>
+          <t>Orgasm and ejaculation: related but distinct</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Xuất tinh gồm 2 giai đoạn thần kinh: Tiết tinh dịch (Emission - chi phối bởi giao cảm T10–L2) và Tống xuất tinh dịch (Expulsion - co thắt cơ hành hang nhịp 0.8s chi phối bởi thần kinh thẹn S2–S4). Sau khi xuất tinh, hormone Prolactin tăng vọt để tắt ham muốn và đưa cơ thể vào thời kỳ trơ sinh lý nhằm bảo vệ hệ tim mạch khỏi kiệt sức.</t>
+          <t>Nếu có thay đổi gây khó chịu, ghi nó xảy ra khi nào, có đau hay không và thuốc đang dùng. Trao đổi với bạn tình để tránh áp lực phải đạt một phản ứng cụ thể; tham khảo chuyên môn nếu vấn đề kéo dài.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Spinal Ejaculatory Generator, Prolactin Surge &amp; Refractory Period</t>
+          <t>Orgasm and ejaculation: related but distinct (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2745,17 +2772,17 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Does Masturbation Affect Testosterone?</t>
+          <t>Masturbation and testosterone myths</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Thủ dâm có ảnh hưởng testosterone?</t>
+          <t>Thủ dâm và testosterone: tránh suy diễn từ biến động ngắn hạn</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Phân biệt myth và bằng chứng</t>
+          <t>Thủ dâm là một hành vi tình dục bình thường nếu tự nguyện và không gây tổn thương hoặc ảnh hưởng đời sống.</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
@@ -2770,17 +2797,17 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/11760788/</t>
+          <t>https://www.devonsexualhealth.nhs.uk/your-sexual-health/relationships-and-intimacy/</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXO_06)</t>
+          <t>Revised — MW_SXO_06; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2790,22 +2817,22 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Thủ Dâm &amp; Nồng Độ Testosterone: Giải Mã Các Lời Đồn Dân Gian Bằng Bằng Chứng Thực Nghiệm</t>
+          <t>Thủ dâm và testosterone: tránh suy diễn từ biến động ngắn hạn</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Masturbation and Testosterone Dynamics: Debunking Myths with Empirical Clinical Trials</t>
+          <t>Masturbation and testosterone myths</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Thủ dâm hay xuất tinh không làm suy giảm nồng độ testosterone nền tảng dài hạn của nam giới. Hiện tượng testosterone tăng vọt vào ngày thứ 7 kiêng cữ chỉ là một đỉnh điều hòa tạm thời trước khi tụt về mức bình thường. Ngược lại, xuất tinh đều đặn ≥ 21 lần/tháng được chứng minh lâm sàng giúp giảm 31% nguy cơ ung thư tuyến tiền liệt.</t>
+          <t>Chọn tần suất theo sự thoải mái, giữ vệ sinh và tránh ma sát gây đau. Nếu hành vi ảnh hưởng ngủ, công việc hoặc cảm giác kiểm soát, trao đổi với chuyên gia mà không cần tự gán một nhãn từ số lần.</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Acute vs Chronic Endocrine Adaptation, Ejaculatory Frequency &amp; Leydig Integrity</t>
+          <t>Masturbation and testosterone myths (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2822,17 +2849,17 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>The Psychology of Performance Anxiety</t>
+          <t>Sexual performance anxiety and communication</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Tâm lý học về lo âu hiệu suất</t>
+          <t>Lo âu khi quan hệ: bớt tự đánh giá, tăng giao tiếp</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Lo âu và trải nghiệm tình dục</t>
+          <t>Lo lắng, mệt mỏi và áp lực thể hiện có thể làm khó hưng phấn hoặc duy trì cương.</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -2847,17 +2874,17 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/16226685/</t>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / DSM-5)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J32" s="15" t="inlineStr">
         <is>
-          <t>Completed (Mapped to DM_MH_03)</t>
+          <t>Revised — DM_MH_03; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2867,22 +2894,22 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Thanh Lọc Tâm Trí &amp; Làm Chủ Thần Kinh Tự Chủ: Vượt Qua Tâm Lý Lo Âu Thực Hiện và Sự Co Mạch Do Cortisol</t>
+          <t>Lo âu khi quan hệ: bớt tự đánh giá, tăng giao tiếp</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Mind Cleaner &amp; Autonomic Mastery: Overcoming Performance Anxiety and Cortisol-Induced Vasoconstriction</t>
+          <t>Sexual performance anxiety and communication</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Lo âu thực hiện (Performance Anxiety) là một cầu dao sinh học: adrenaline từ hệ giao cảm sẽ khóa chặt động mạch dương vật thông qua cơ chế co mạch alpha-adrenergic. Giải tỏa dòng suy nghĩ căng thẳng bằng 5–10 phút Viết Tự Do (Expressive Freewriting)—kết hợp 3 chu kỳ Tiếng Thở Dài Sinh Lý—sẽ khôi phục chỉ số HRV phế vị và kích hoạt giãn mạch bằng oxit nitric.</t>
+          <t>Thử thống nhất những buổi gần gũi không đặt mục tiêu phải giao hợp hoặc cực khoái. Nói rõ cảm giác, lựa chọn thoải mái và quyền dừng lại. Nếu lo lắng dai dẳng, tìm hỗ trợ trị liệu phù hợp.</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Stress Management Score, Autonomic Nervous System &amp; Sensate Focus</t>
+          <t>Sexual performance anxiety and communication (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2926,17 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>How Sexual Desire Changes With Age</t>
+          <t>Sexual desire with age</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Ham muốn thay đổi theo tuổi thế nào?</t>
+          <t>Ham muốn và tuổi tác: thay đổi không đồng nghĩa phải chịu đựng</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Tuổi tác và các yếu tố liên quan</t>
+          <t>Ham muốn và phản ứng tình dục có thể thay đổi theo tuổi, sức khỏe, thuốc và quan hệ; không có mức suy giảm tất yếu giống nhau cho tất cả.</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -2924,17 +2951,17 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/11836290/</t>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Verified &amp; Peer-Reviewed (PubMed / NIH / Guidelines)</t>
+          <t>Source replaced / checked; see master Editorial_Audit</t>
         </is>
       </c>
       <c r="J33" s="15" t="inlineStr">
         <is>
-          <t>Completed (Written &amp; Published as MW_SXO_08)</t>
+          <t>Revised — MW_SXO_08; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2944,22 +2971,22 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ham Muốn &amp; Tuổi Tác: Thích Ứng Với Sự Giảm Testosterone Tự Nhiên &amp; Nâng Tầm Chất Lượng</t>
+          <t>Ham muốn và tuổi tác: thay đổi không đồng nghĩa phải chịu đựng</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Sexual Dynamics Across Aging: Navigating Andropause, Hormonal Shifts &amp; Redefining Intimacy</t>
+          <t>Sexual desire with age</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Từ tuổi 30, Testosterone tự do giảm khoảng 1%–2% mỗi năm chủ yếu do protein mang SHBG gia tăng. Cơ thể cần thời gian kích thích trực tiếp lâu hơn và thời kỳ trơ sau xuất tinh kéo dài hơn. Duy trì thể lực tim mạch, kiểm soát mỡ bụng và mở rộng định nghĩa tình dục vượt ra ngoài việc xâm nhập thuần túy giúp duy trì bản lĩnh tới tuổi 70–80.</t>
+          <t>Nói rõ điều bạn muốn cải thiện, triệu chứng và thuốc với bác sĩ. Trao đổi về hình thức thân mật, thời gian và sự thoải mái với bạn tình. Chăm sóc sức khỏe chung trước khi tìm sản phẩm chống lão hóa sinh lý.</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Age-Related Androgen Decline (-1%/year), SHBG Elevation &amp; Redefining Intimacy</t>
+          <t>Sexual desire with age (educational topic; not a measured biomarker)</t>
         </is>
       </c>
     </row>
@@ -2972,9 +2999,43 @@
       <formula1>"Planned,Researching,Writing,Medical Review,Published"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId33"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2986,7 +3047,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -3141,4 +3202,2682 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Content_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Title_VI</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Title_EN</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Source_Name</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Source_URL</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Public_URL</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>Review_Status</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>Limits_VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="86" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>LM_MH_01</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>Sàn chậu nam: hỗ trợ tiểu tiện và chức năng tình dục</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>The male pelvic floor: support and function</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>North Tees and Hartlepool NHS — Pelvic Floor Exercises for Men</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nth.nhs.uk/resources/pelvic-floor-exercises-for-men/</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/LM_MH_01.html</t>
+        </is>
+      </c>
+      <c r="G2" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H2" s="19" t="inlineStr">
+        <is>
+          <t>Cơ sàn chậu không phải yếu tố duy nhất quyết định độ cương. Không dùng thường xuyên cách ngắt dòng tiểu để tập và không tập siết tối đa cả ngày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="86" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>LM_MH_02</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Kegel cho nam: co nhẹ, thở đều và thả lỏng đủ</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Kegel technique for men</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>North Tees and Hartlepool NHS — Pelvic Floor Exercises for Men</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nth.nhs.uk/resources/pelvic-floor-exercises-for-men/</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/LM_MH_02.html</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>Không có một lịch giữ–nghỉ áp dụng cho tất cả. Tránh tập bằng cách ngắt dòng tiểu thường xuyên hoặc cố siết khi đang đau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="86" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>LM_MH_03</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Kegel có chữa rối loạn cương hoặc xuất tinh sớm không?</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>Can pelvic-floor exercises treat sexual difficulties?</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>Royal Berkshire NHS (2024) — Pelvic floor strengthening and relaxation exercises for men</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>https://www.royalberkshire.nhs.uk/media/avwg3hls/pelvic-floor-strengthening-and-relaxation-exercises-for-men_jun24.pdf</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/LM_MH_03.html</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>Không hứa tỷ lệ chữa khỏi hay số tuần cải thiện từ một nghiên cứu nhỏ. Tăng số lần siết không bảo đảm giúp và có thể không phù hợp khi cơ đã căng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="86" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>DM_MH_01</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Xuất tinh sớm: giảm áp lực và tìm cách hỗ trợ phù hợp</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Premature ejaculation: reducing pressure and finding support</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Ejaculation problems</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/conditions/ejaculation-problems/</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/DM_MH_01.html</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>Không có bằng chứng đủ mạnh để hứa một cú siết Kegel sẽ khóa phản xạ xuất tinh. Tránh gồng tối đa, nín thở hoặc rặn mạnh như một kỹ thuật bắt buộc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="86" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>DM_MH_02</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Giãn cơ vùng háng và đau chậu: biết khi nào nên dừng</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Groin mobility and pelvic discomfort</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Royal Berkshire NHS (2024) — Pelvic floor strengthening and relaxation exercises for men</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>https://www.royalberkshire.nhs.uk/media/avwg3hls/pelvic-floor-strengthening-and-relaxation-exercises-for-men_jun24.pdf</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/DM_MH_02.html</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>Không kéo mạnh để cố mở vùng chậu hoặc dùng bài giãn như điều trị rối loạn cương. Người có cơ sàn chậu quá căng có thể cần chương trình riêng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="86" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>DM_MH_03</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Lo âu khi quan hệ: bớt tự đánh giá, tăng giao tiếp</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Sexual performance anxiety and communication</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>NIDDK — Symptoms &amp; Causes of Erectile Dysfunction</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/DM_MH_03.html</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>HRV thấp không xác định lo âu thực hiện hay độc tính cortisol. Thở và thư giãn có thể hỗ trợ, nhưng không bảo đảm khắc phục mọi nguyên nhân rối loạn cương.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="86" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>MW_NUT_01</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Ăn uống và testosterone: ưu tiên đủ chất, tránh lời hứa tăng hormone</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Diet and testosterone: adequacy before boosters</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>WHO — Healthy diet</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/healthy-diet</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_NUT_01.html</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>Không có tỷ lệ chất béo hay ngưỡng thâm hụt calo duy nhất giữ testosterone tối ưu cho tất cả. Bệnh lý cần đánh giá triệu chứng cùng xét nghiệm phù hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="86" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>MW_NUT_02</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Ăn kiểu Địa Trung Hải: một cách xây bữa ăn lành mạnh</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Mediterranean-style eating and men's health</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>WHO — Healthy diet</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/healthy-diet</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_NUT_02.html</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>Không gọi chế độ ăn là lá chắn bảo đảm khỏi bệnh hoặc thuốc chữa rối loạn cương. Hiệu quả sức khỏe phụ thuộc cả lối sống và bệnh nền.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="86" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>MW_NUT_03</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Cần bao nhiêu protein khi tập sức mạnh?</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Protein needs for resistance training</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Morton et al. (2018) — A systematic review, meta-analysis and meta-regression of the effect of protein supplementation on resistance training-induced gains in muscle mass and strength in healthy adults</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28698222/</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_NUT_03.html</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>Nghiên cứu không chứng minh ăn càng nhiều càng tăng cơ, cũng không cho phép kết luận an toàn ở mọi bệnh thận. Nhu cầu thay đổi theo mục tiêu và bối cảnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="86" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>MW_NUT_04</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Rượu bia và phục hồi: giảm rủi ro thay vì tìm liều có lợi</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Alcohol and recovery</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>WHO — Alcohol</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/alcohol</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_NUT_04.html</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>Một đêm nhịp tim cao không cho biết testosterone đã giảm bao nhiêu. Không quy đổi số ly thành phần trăm hormone hay tổn hại cố định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="86" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXH_01</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Testosterone thấp: chẩn đoán cần hơn một con số</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Understanding low testosterone testing</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Bhasin et al. (2018) — Testosterone Therapy in Men With Hypogonadism: An Endocrine Society Clinical Practice Guideline</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29562364/</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXH_01.html</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>Khoảng tham chiếu phụ thuộc labo; total T và free T không hoán đổi trực tiếp. Không dùng dữ liệu thiết bị đeo để chẩn đoán thiếu testosterone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="86" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXH_02</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Rối loạn cương: dấu hiệu nên được đánh giá toàn diện</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Erectile dysfunction and whole-person assessment</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>NIDDK — Symptoms &amp; Causes of Erectile Dysfunction</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXH_02.html</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>Rối loạn cương không có nghĩa chắc sắp bị nhồi máu cơ tim, và không phải mọi trường hợp đều do testosterone thấp. Tự mua thuốc có thể bỏ sót nguyên nhân.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="86" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXH_03</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Thiếu ngủ và testosterone: không quy đổi thành số năm già đi</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Sleep restriction and testosterone: interpreting the evidence</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Leproult &amp; Van Cauter (2011) — Effect of 1 week of sleep restriction on testosterone levels in young healthy men</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/21632481/</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXH_03.html</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>Không chuyển kết quả thử nghiệm nhỏ thành tỷ lệ giảm cố định theo từng giờ thiếu ngủ. Điểm ngủ không đo testosterone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="86" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXH_04</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Stress và chức năng tình dục nam: tránh tự chẩn đoán cortisol</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Stress and male sexual function</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>NIDDK — Symptoms &amp; Causes of Erectile Dysfunction</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXH_04.html</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
+        <is>
+          <t>Không dùng HRV hay cảm giác căng để suy ra tỷ lệ hormone. Kỹ thuật thư giãn có thể hỗ trợ nhưng không thay điều trị nguyên nhân y khoa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="86" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>MW_REL_01</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Giao tiếp cặp đôi: bắt đầu từ một cuộc trò chuyện cụ thể</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Practical communication in a relationship</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Maintaining healthy relationships and mental wellbeing</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_REL_01.html</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H16" s="19" t="inlineStr">
+        <is>
+          <t>Đây là gợi ý giao tiếp, không phải công thức điều trị hay bằng chứng điều chỉnh oxytocin. Không dùng bài tập để ép đối phương chấp nhận yêu cầu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="86" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>MW_REL_02</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Mở lời về tình dục: mong muốn, ranh giới và sự đồng thuận</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Talking about sex, preferences and boundaries</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Mallory et al. (2019) — Couples' Sexual Communication and Dimensions of Sexual Function: A Meta-Analysis</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30777780/</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_REL_02.html</t>
+        </is>
+      </c>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>Liên hệ thống kê không bảo đảm hiệu quả cho từng cặp. Im lặng, kích thích cơ thể hoặc đã đồng ý trước đó không thay cho sự đồng thuận hiện tại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="86" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>MW_REL_03</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Thân mật cảm xúc: xây từ sự quan tâm hằng ngày</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Building emotional intimacy</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Maintaining healthy relationships and mental wellbeing</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_REL_03.html</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>Đây là gợi ý thực hành quan hệ, không phải phác đồ tăng oxytocin. Không có mức tiết lộ cảm xúc bắt buộc hoặc tiến độ chuẩn cho mọi cặp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="86" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>MW_REL_04</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Khi stress lan vào mối quan hệ: nói rõ nhu cầu hỗ trợ</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>When stress affects a relationship</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Maintaining healthy relationships and mental wellbeing</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_REL_04.html</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="inlineStr">
+        <is>
+          <t>Không gán mọi xung đột cho hệ thần kinh hay cortisol. Các bài tự giúp không thay giải quyết hành vi thiếu tôn trọng hoặc điều kiện sống gây áp lực.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="86" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXO_01</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Ham muốn nam giới: không chỉ là testosterone</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Male sexual desire beyond testosterone</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Low sex drive (loss of libido)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXO_01.html</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>Không dùng nhịp tim hoặc HRV để chấm ham muốn hay nồng độ dopamine. Không có tần suất tình dục chuẩn cho mọi người.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="86" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXO_02</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Hưng phấn và cương: phản ứng cơ thể không thay cho đồng thuận</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>Arousal, erections and consent</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>NIDDK — Symptoms &amp; Causes of Erectile Dysfunction</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXO_02.html</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
+        <is>
+          <t>Một lần không cương không xác định bệnh, thiếu hấp dẫn hay thiếu testosterone. Cũng không thể suy độ cương từ cảm biến nhịp tim phổ thông.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="86" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXO_03</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Ham muốn thấp có luôn là testosterone thấp?</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Does low desire always mean low testosterone?</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Low sex drive (loss of libido)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXO_03.html</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>Một mức testosterone trong khoảng tham chiếu không giải thích hết đời sống tình dục. Tăng nồng độ ở người không thiếu không bảo đảm tăng hài lòng hoặc ham muốn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="86" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXO_04</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Có mức ham muốn bình thường cho tất cả không?</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Is there a normal amount of sexual desire?</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Low sex drive (loss of libido)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXO_04.html</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H23" s="19" t="inlineStr">
+        <is>
+          <t>Mô hình lý thuyết về kích thích và ức chế không chẩn đoán được từng người. Không suy chất lượng quan hệ từ số lần quan hệ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="86" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>MW_NUT_05</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>Kẽm và vitamin D: bổ sung theo nhu cầu, không theo lời hứa tăng T</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Zinc and vitamin D: needs rather than hormone promises</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>NIH ODS — Zinc: Health Professional Fact Sheet</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>https://ods.od.nih.gov/factsheets/Zinc-HealthProfessional/</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_NUT_05.html</t>
+        </is>
+      </c>
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H24" s="19" t="inlineStr">
+        <is>
+          <t>Dùng dư có thể gây hại và tương tác thuốc; kẽm kéo dài liều cao có thể ảnh hưởng đồng. Không áp dụng liều điều trị thiếu hụt cho người chưa được đánh giá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="86" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>MW_NUT_06</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Dinh dưỡng và chất lượng tinh trùng: hiểu giới hạn bằng chứng</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>Nutrition and sperm health: evidence limits</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>AUA/ASRM — Diagnosis and treatment of infertility in men: guideline part II</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>https://integration.asrm.org/practice-guidance/practice-committee-documents/diagnosis-and-treatment-of-infertility-in-men-aua-asrm-guideline-part2/</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_NUT_06.html</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H25" s="19" t="inlineStr">
+        <is>
+          <t>Không hứa một thực phẩm cải thiện DNA tinh trùng hay tăng xác suất có con theo tỷ lệ cố định. Nghiên cứu quan sát về ăn uống không chứng minh hiệu quả điều trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="86" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>MW_NUT_07</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Nhịn ăn gián đoạn và hormone nam: còn nhiều điều chưa chắc chắn</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>Intermittent fasting and male hormones</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>Cienfuegos et al. (2022) — Effect of Intermittent Fasting on Reproductive Hormone Levels in Females and Males: A Review of Human Trials</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35684143/</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_NUT_07.html</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H26" s="19" t="inlineStr">
+        <is>
+          <t>Không suy mọi thay đổi từ thời gian nhịn riêng lẻ; tổng năng lượng và thành phần bữa ăn cũng khác giữa nghiên cứu. Tín hiệu hormone không tự xác định bệnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="86" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>MW_NUT_08</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Bù nước khi vận động: đáp ứng nhu cầu thay vì ép một công thức</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>Hydration during activity</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Dehydration</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/conditions/dehydration/</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_NUT_08.html</t>
+        </is>
+      </c>
+      <c r="G27" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="inlineStr">
+        <is>
+          <t>Không có một công thức ml/kg hay mức giảm 2% bảo đảm dự báo hiệu suất ở tất cả. Người có chỉ định hạn chế dịch phải theo đội ngũ điều trị.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="86" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXH_05</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Cương buổi sáng: một dấu hiệu, không phải bài kiểm tra hormone</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>Morning erections and what they mean</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>NIDDK — Symptoms &amp; Causes of Erectile Dysfunction</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXH_05.html</t>
+        </is>
+      </c>
+      <c r="G28" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H28" s="19" t="inlineStr">
+        <is>
+          <t>Có cương sáng không loại trừ mọi nguyên nhân rối loạn cương. Thiết bị theo dõi giấc ngủ phổ thông không đo được độ cương hay nồng độ hormone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="86" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXH_06</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Vận động và chức năng cương: hỗ trợ sức khỏe chung</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>Physical activity and erectile health</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>NIDDK — Treatment for Erectile Dysfunction</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/treatment</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXH_06.html</t>
+        </is>
+      </c>
+      <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="inlineStr">
+        <is>
+          <t>Không dùng tần suất quan hệ hay một biến động hormone sau tập để đánh giá hiệu quả vận động. Tập quá mức khi thiếu năng lượng cũng không có lợi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="86" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXH_07</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>Sinh sản nam: chú ý sức khỏe, thuốc và đánh giá phù hợp</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>Male fertility: health, medicines and assessment</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>AUA/ASRM — Diagnosis and treatment of infertility in men: guideline part II</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>https://integration.asrm.org/practice-guidance/practice-committee-documents/diagnosis-and-treatment-of-infertility-in-men-aua-asrm-guideline-part2/</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXH_07.html</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="inlineStr">
+        <is>
+          <t>Không hứa rằng chờ đúng một chu kỳ sinh tinh hoặc tránh một nguồn nhiệt sẽ khắc phục mọi vấn đề. Một xét nghiệm tinh dịch riêng lẻ không bảo đảm khả năng có con.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="86" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXH_08</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Khi nào nên xét nghiệm testosterone?</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>When testosterone testing is appropriate</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Bhasin et al. (2018) — Testosterone Therapy in Men With Hypogonadism: An Endocrine Society Clinical Practice Guideline</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29562364/</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXH_08.html</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
+        <is>
+          <t>Không đặt chẩn đoán từ một kết quả hoặc một khoảng tham chiếu trên mạng. Free T, total T và các xét nghiệm liên quan cần được diễn giải theo tình huống.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="86" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>MW_REL_05</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>Tranh luận ít gây tổn thương hơn: tạm dừng và quay lại vấn đề</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>Managing disagreements with less harm</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Maintaining healthy relationships and mental wellbeing</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_REL_05.html</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="inlineStr">
+        <is>
+          <t>Khoảng nghỉ không được dùng như phạt im lặng hoặc né tránh vô thời hạn. Đây không phải công thức điều trị cho mọi kiểu xung đột.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="86" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>MW_REL_06</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>Khi hai người có mức ham muốn khác nhau</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>When partners want different amounts of sex</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Low sex drive (loss of libido)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_REL_06.html</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H33" s="19" t="inlineStr">
+        <is>
+          <t>Khái niệm ham muốn đáp ứng không có nghĩa nên bắt đầu hoạt động không mong muốn để rồi tự thích. Không biến mô hình tâm lý thành nghĩa vụ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="86" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>MW_REL_07</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>Lòng tin: bắt đầu bằng hành vi có thể quan sát</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>Trust through observable actions</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Maintaining healthy relationships and mental wellbeing</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_REL_07.html</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H34" s="19" t="inlineStr">
+        <is>
+          <t>Đây là gợi ý thực hành, không phải thời hạn bảo đảm xây lại lòng tin. Kiểm tra điện thoại hoặc theo dõi dữ liệu cơ thể không phải bằng chứng cần thiết của sự chung thủy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="86" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>MW_REL_08</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Giấc ngủ và mối quan hệ: cùng tìm cách nghỉ phù hợp</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>Sleep and relationships</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>The association between couple relationships and sleep: A systematic review and meta-analysis</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39514915/</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_REL_08.html</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H35" s="19" t="inlineStr">
+        <is>
+          <t>Không suy quan hệ tốt hay xấu từ việc ngủ chung hoặc điểm ngủ giống nhau. Một đêm thiếu ngủ không tất yếu gây xung đột.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="86" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXO_05</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>Cực khoái và xuất tinh: có liên quan nhưng không hoàn toàn giống nhau</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>Orgasm and ejaculation: related but distinct</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Ejaculation problems</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/conditions/ejaculation-problems/</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXO_05.html</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H36" s="19" t="inlineStr">
+        <is>
+          <t>Không có thời kỳ trơ chuẩn cho mọi nam giới hoặc mẹo bảo đảm rút ngắn. Lượng tinh dịch không đo chất lượng cực khoái hay mức testosterone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="86" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXO_06</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Thủ dâm và testosterone: tránh suy diễn từ biến động ngắn hạn</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>Masturbation and testosterone myths</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Devon Sexual Health (NHS) — Relationships and intimacy</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>https://www.devonsexualhealth.nhs.uk/your-sexual-health/relationships-and-intimacy/</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXO_06.html</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H37" s="19" t="inlineStr">
+        <is>
+          <t>Không có lịch kiêng bắt buộc để giữ nam tính, cơ bắp hay mức testosterone bình thường. Nội dung về hành vi không thay đánh giá y khoa nếu có triệu chứng thiếu hormone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="86" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>MW_SXO_08</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Ham muốn và tuổi tác: thay đổi không đồng nghĩa phải chịu đựng</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>Sexual desire with age</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Low sex drive (loss of libido)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>https://test-repo-y1wb.onrender.com/posts/MW_SXO_08.html</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>Revised against cited sources; clinical sign-off not recorded</t>
+        </is>
+      </c>
+      <c r="H38" s="19" t="inlineStr">
+        <is>
+          <t>Không chẩn đoán thiếu testosterone từ tuổi hoặc ham muốn đơn lẻ. Điều trị hormone không phải mặc định cho mọi nam giới lớn tuổi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H38"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId74"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Source_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Supports_VI</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Supports_EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="86" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>pelvic_men</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>North Tees and Hartlepool NHS — Pelvic Floor Exercises for Men</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nth.nhs.uk/resources/pelvic-floor-exercises-for-men/</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>Physiotherapy patient guidance</t>
+        </is>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>Nhận biết, co và thả lỏng cơ sàn chậu nam</t>
+        </is>
+      </c>
+      <c r="F2" s="19" t="inlineStr">
+        <is>
+          <t>Identifying, contracting and relaxing male pelvic floor muscles</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="86" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>pelvic_relax</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Royal Berkshire NHS (2024) — Pelvic floor strengthening and relaxation exercises for men</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>https://www.royalberkshire.nhs.uk/media/avwg3hls/pelvic-floor-strengthening-and-relaxation-exercises-for-men_jun24.pdf</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>Physiotherapy patient guidance</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>Phối hợp tăng sức mạnh và thả lỏng; không kê bài siết cho tất cả</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>Strengthening and relaxation; not a prescription to tighten for everyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="86" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>ed</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>NIDDK — Symptoms &amp; Causes of Erectile Dysfunction</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/symptoms-causes</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>Nguyên nhân mạch máu, thần kinh, thuốc và tâm lý của rối loạn cương</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>Vascular, neurological, medication and psychological causes of ED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="86" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>ed_treatment</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>NIDDK — Treatment for Erectile Dysfunction</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/treatment</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Chăm sóc theo nguyên nhân; thay đổi lối sống và điều trị chuyên môn</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>Cause-based care, lifestyle changes and professional treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="86" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>ejaculation</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Ejaculation problems</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/conditions/ejaculation-problems/</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Các rối loạn xuất tinh và lựa chọn điều trị</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Ejaculatory difficulties and treatment options</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="86" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>sexual_health</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Devon Sexual Health (NHS) — Relationships and intimacy</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>https://www.devonsexualhealth.nhs.uk/your-sexual-health/relationships-and-intimacy/</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Sexual health service guidance</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Đồng thuận, thân mật và thủ dâm</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Consent, intimacy and masturbation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="86" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>testicle</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Testicle pain</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/symptoms/testicle-pain/</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Đau tinh hoàn đột ngột hoặc nặng cần chăm sóc khẩn</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Sudden or severe testicular pain requires urgent care</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="86" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>diet</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>WHO — Healthy diet</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/healthy-diet</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Chế độ ăn đa dạng và chất lượng thực phẩm</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Dietary variety and food quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="86" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>hypogonadism</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Endocrine Society — Hypogonadism in Men</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>https://www.endocrine.org/patient-engagement/endocrine-library/hypogonadism</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Professional patient guidance</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Chẩn đoán thiếu testosterone và giới hạn xét nghiệm</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Low testosterone diagnosis and testing limitations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="86" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>reds</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Mountjoy et al. (2023) — IOC consensus statement on Relative Energy Deficiency in Sport (REDs)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>https://bjsm.bmj.com/content/57/17/1073</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Consensus statement</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Thiếu năng lượng, xương, kinh nguyệt và đánh giá đa chuyên ngành</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>Low energy availability, bone, menstrual health and multidisciplinary assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="86" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Morton et al. (2018) — A systematic review, meta-analysis and meta-regression of the effect of protein supplementation on resistance training-induced gains in muscle mass and strength in healthy adults</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28698222/</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Systematic review and meta-analysis</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Protein và tập kháng lực ở người khỏe mạnh; không áp dụng trực tiếp cho bệnh thận</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>Protein with resistance training in healthy adults; not directly applicable to kidney disease</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="86" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>WHO — Alcohol</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/alcohol</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Public health evidence summary</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Nguy cơ sức khỏe từ rượu; không có mức uống hoàn toàn không rủi ro</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>Alcohol-related health risks; no completely risk-free consumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="86" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>sleep_habits</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>NHLBI — Healthy Sleep Habits</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhlbi.nih.gov/health/sleep-deprivation/healthy-sleep-habits</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Thói quen ngủ và lịch sinh hoạt</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>Sleep habits and consistent schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="86" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>testosterone</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Bhasin et al. (2018) — Testosterone Therapy in Men With Hypogonadism: An Endocrine Society Clinical Practice Guideline</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29562364/</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Clinical practice guideline</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Triệu chứng cộng xét nghiệm buổi sáng lặp lại; tránh testosterone khi muốn có con</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>Symptoms plus repeated morning tests; avoid testosterone when planning fertility</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="86" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>male_fertility</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>AUA/ASRM — Diagnosis and treatment of infertility in men: guideline part II</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>https://integration.asrm.org/practice-guidance/practice-committee-documents/diagnosis-and-treatment-of-infertility-in-men-aua-asrm-guideline-part2/</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Clinical practice guideline</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Giới hạn bằng chứng của chất bổ sung và tác động testosterone đến sinh sản</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>Limited supplement evidence and testosterone-related fertility concerns</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="86" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>sleep_t</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Leproult &amp; Van Cauter (2011) — Effect of 1 week of sleep restriction on testosterone levels in young healthy men</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/21632481/</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Small experimental study</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Thử nghiệm nhỏ ở nam trẻ; không quy đổi thiếu ngủ thành tuổi già</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>Small study in young men; does not translate sleep loss into years of ageing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="86" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>sleep_length</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>NHLBI — How Much Sleep Is Enough?</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhlbi.nih.gov/health/sleep/how-much-sleep</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Thời lượng ngủ theo tuổi; nợ ngủ</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>Age-related sleep needs; sleep debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="86" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>apnea</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>NHLBI — Sleep Apnea Symptoms</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhlbi.nih.gov/health/sleep-apnea/symptoms</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Ngáy, ngưng thở và buồn ngủ ban ngày</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>Snoring, breathing pauses and daytime sleepiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="86" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>libido</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Low sex drive (loss of libido)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Nhiều yếu tố ảnh hưởng ham muốn và chăm sóc theo nguyên nhân</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>Multiple influences on desire and cause-based care</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="86" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>relationships</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Maintaining healthy relationships and mental wellbeing</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/every-mind-matters/lifes-challenges/maintaining-healthy-relationships-and-mental-wellbeing/</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Giao tiếp, ranh giới và ứng phó bất đồng</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>Communication, boundaries and managing disagreements</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="86" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Mallory et al. (2019) — Couples' Sexual Communication and Dimensions of Sexual Function: A Meta-Analysis</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30777780/</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>Meta-analysis of associations</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Liên hệ giữa giao tiếp và chức năng tình dục; không chứng minh nhân quả</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>Association of communication and sexual function; not proof of causation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="86" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>couple_sleep</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>The association between couple relationships and sleep: A systematic review and meta-analysis</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39514915/</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Systematic review and meta-analysis</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Liên hệ hai chiều có thể có giữa giấc ngủ và chất lượng quan hệ</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Associations between sleep and relationship quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="86" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>NIH ODS — Zinc: Health Professional Fact Sheet</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>https://ods.od.nih.gov/factsheets/Zinc-HealthProfessional/</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>Evidence fact sheet</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Nhu cầu kẽm, thiếu hụt và tác hại khi dư</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr">
+        <is>
+          <t>Zinc needs, deficiency and excess toxicity</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="86" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>NIH ODS — Vitamin D: Fact Sheet for Consumers</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>https://ods.od.nih.gov/factsheets/VitaminD-Consumer/</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Evidence fact sheet</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Vai trò vitamin D và nguy cơ dùng quá mức</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>Vitamin D roles and excessive intake risks</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="86" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>natural_fertility</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>ASRM (2022) — Optimizing natural fertility: a committee opinion</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>https://integration.asrm.org/globalassets/_asrm/practice-guidance/practice-guidelines/pdf/optimizing_natural_fertility.pdf</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>Committee opinion</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Thời điểm quan hệ, giới hạn dự đoán và khi đánh giá hiếm muộn</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>Intercourse timing, prediction limitations and fertility evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="86" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>fasting</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Cienfuegos et al. (2022) — Effect of Intermittent Fasting on Reproductive Hormone Levels in Females and Males: A Review of Human Trials</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35684143/</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Review of human trials</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Nghiên cứu hormone còn ít; không thể hứa tăng testosterone</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>Limited hormone trials; no basis to promise a testosterone increase</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="86" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>hydration</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Dehydration</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/conditions/dehydration/</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Dấu hiệu mất nước và khi cần chăm sóc khẩn</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>Dehydration symptoms and when urgent care is needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="86" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>activity</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>WHO — Physical activity</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/physical-activity</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Public health guideline summary</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Khuyến nghị vận động theo nhóm đối tượng</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>Activity recommendations by population</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F29"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/Mens_Wellness_Content_Roadmap.xlsx
+++ b/docs/Mens_Wellness_Content_Roadmap.xlsx
@@ -10,7 +10,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reviewed_Content'!$A$1:$H$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Source_Register'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Source_Register'!$A$1:$F$52</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G2" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H2" s="19" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="G3" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H3" s="19" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>Royal Berkshire NHS (2024) — Pelvic floor strengthening and relaxation exercises for men</t>
+          <t>Dorey et al. (2004) — Randomised controlled trial of pelvic floor muscle exercises and manometric biofeedback for erectile dysfunction</t>
         </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>https://www.royalberkshire.nhs.uk/media/avwg3hls/pelvic-floor-strengthening-and-relaxation-exercises-for-men_jun24.pdf</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/15527607/</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H4" s="19" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H5" s="19" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H7" s="19" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H13" s="19" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H15" s="19" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H21" s="19" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="G23" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H23" s="19" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H25" s="19" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H27" s="19" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H29" s="19" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H31" s="19" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H33" s="19" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="G35" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H35" s="19" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="G36" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H36" s="19" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="G37" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H37" s="19" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>Revised against cited sources; clinical sign-off not recorded</t>
+          <t>Long-form development of original outline; sources checked; clinical sign-off not recorded</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5049,17 +5049,17 @@
     <row r="5" ht="86" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>ed_treatment</t>
+          <t>pelvic_women</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>NIDDK — Treatment for Erectile Dysfunction</t>
+          <t>NHS — Urinary incontinence: non-surgical treatment</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/treatment</t>
+          <t>https://www.nhs.uk/conditions/urinary-incontinence/treatment/</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -5069,93 +5069,93 @@
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>Chăm sóc theo nguyên nhân; thay đổi lối sống và điều trị chuyên môn</t>
+          <t>Đánh giá sàn chậu và tập có giám sát cho rò tiểu</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>Cause-based care, lifestyle changes and professional treatment</t>
+          <t>Pelvic-floor assessment and supervised training for leakage</t>
         </is>
       </c>
     </row>
     <row r="6" ht="86" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>ejaculation</t>
+          <t>pelvic_women_relax</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>NHS — Ejaculation problems</t>
+          <t>Cambridge University Hospitals — Female pelvic floor muscle exercises</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>https://www.nhs.uk/conditions/ejaculation-problems/</t>
+          <t>https://www.cuh.nhs.uk/patient-information/female-pelvic-floor-muscle-exercises/</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Public health guidance</t>
+          <t>Physiotherapy patient guidance</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>Các rối loạn xuất tinh và lựa chọn điều trị</t>
+          <t>Cần thả lỏng đầy đủ giữa các lần co cơ</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>Ejaculatory difficulties and treatment options</t>
+          <t>Full relaxation between pelvic-floor contractions</t>
         </is>
       </c>
     </row>
     <row r="7" ht="86" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>sexual_health</t>
+          <t>pelvic_review</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Devon Sexual Health (NHS) — Relationships and intimacy</t>
+          <t>Cohen et al. (2016) — The Role of Pelvic Floor Muscles in Male Sexual Dysfunction and Pelvic Pain</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>https://www.devonsexualhealth.nhs.uk/your-sexual-health/relationships-and-intimacy/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27872005/</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Sexual health service guidance</t>
+          <t>Clinical review</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>Đồng thuận, thân mật và thủ dâm</t>
+          <t>Quan hệ giải phẫu, chức năng sàn chậu và tiếp cận sinh học–tâm lý–xã hội</t>
         </is>
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>Consent, intimacy and masturbation</t>
+          <t>Pelvic anatomy, function and a biopsychosocial approach</t>
         </is>
       </c>
     </row>
     <row r="8" ht="86" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>testicle</t>
+          <t>ed_treatment</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>NHS — Testicle pain</t>
+          <t>NIDDK — Treatment for Erectile Dysfunction</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>https://www.nhs.uk/symptoms/testicle-pain/</t>
+          <t>https://www.niddk.nih.gov/health-information/urologic-diseases/erectile-dysfunction/treatment</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
@@ -5165,317 +5165,317 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>Đau tinh hoàn đột ngột hoặc nặng cần chăm sóc khẩn</t>
+          <t>Chăm sóc theo nguyên nhân; thay đổi lối sống và điều trị chuyên môn</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>Sudden or severe testicular pain requires urgent care</t>
+          <t>Cause-based care, lifestyle changes and professional treatment</t>
         </is>
       </c>
     </row>
     <row r="9" ht="86" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>diet</t>
+          <t>sexual_health</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>WHO — Healthy diet</t>
+          <t>Devon Sexual Health (NHS) — Relationships and intimacy</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>https://www.who.int/news-room/fact-sheets/detail/healthy-diet</t>
+          <t>https://www.devonsexualhealth.nhs.uk/your-sexual-health/relationships-and-intimacy/</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Public health guidance</t>
+          <t>Sexual health service guidance</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>Chế độ ăn đa dạng và chất lượng thực phẩm</t>
+          <t>Đồng thuận, thân mật và thủ dâm</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>Dietary variety and food quality</t>
+          <t>Consent, intimacy and masturbation</t>
         </is>
       </c>
     </row>
     <row r="10" ht="86" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>hypogonadism</t>
+          <t>lue_review</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Endocrine Society — Hypogonadism in Men</t>
+          <t>Lue (2000) — Erectile dysfunction</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>https://www.endocrine.org/patient-engagement/endocrine-library/hypogonadism</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/10853004/</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>Professional patient guidance</t>
+          <t>Clinical physiology review</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>Chẩn đoán thiếu testosterone và giới hạn xét nghiệm</t>
+          <t>Cơ chế thần kinh–mạch máu của cương và đường NO/cGMP</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>Low testosterone diagnosis and testing limitations</t>
+          <t>Neurovascular erection physiology and the NO/cGMP pathway</t>
         </is>
       </c>
     </row>
     <row r="11" ht="86" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>reds</t>
+          <t>breathing</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Mountjoy et al. (2023) — IOC consensus statement on Relative Energy Deficiency in Sport (REDs)</t>
+          <t>Zaccaro et al. (2018) — How Breath-Control Can Change Your Life: A Systematic Review on Psycho-Physiological Correlates of Slow Breathing</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>https://bjsm.bmj.com/content/57/17/1073</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30245619/</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>Consensus statement</t>
+          <t>Systematic review</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>Thiếu năng lượng, xương, kinh nguyệt và đánh giá đa chuyên ngành</t>
+          <t>Thở chậm, HRV và nghiên cứu không đồng nhất</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>Low energy availability, bone, menstrual health and multidisciplinary assessment</t>
+          <t>Slow breathing, HRV and heterogeneous evidence</t>
         </is>
       </c>
     </row>
     <row r="12" ht="86" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>protein</t>
+          <t>hrv_measure</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Morton et al. (2018) — A systematic review, meta-analysis and meta-regression of the effect of protein supplementation on resistance training-induced gains in muscle mass and strength in healthy adults</t>
+          <t>Draghici &amp; Taylor (2016) — The physiological basis and measurement of heart rate variability in humans</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/28698222/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27680542/</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>Systematic review and meta-analysis</t>
+          <t>Physiology review</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>Protein và tập kháng lực ở người khỏe mạnh; không áp dụng trực tiếp cho bệnh thận</t>
+          <t>Cơ chế và giới hạn diễn giải HRV</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>Protein with resistance training in healthy adults; not directly applicable to kidney disease</t>
+          <t>Mechanisms and interpretation limits of HRV</t>
         </is>
       </c>
     </row>
     <row r="13" ht="86" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>cooldown</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>WHO — Alcohol</t>
+          <t>Van Hooren &amp; Peake (2018) — Do We Need a Cool-Down After Exercise?</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>https://www.who.int/news-room/fact-sheets/detail/alcohol</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29663142/</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Public health evidence summary</t>
+          <t>Narrative review</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>Nguy cơ sức khỏe từ rượu; không có mức uống hoàn toàn không rủi ro</t>
+          <t>Hạn chế bằng chứng về giảm đau cơ và phục hồi nhờ hạ nhiệt chủ động</t>
         </is>
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>Alcohol-related health risks; no completely risk-free consumption</t>
+          <t>Limited evidence for active cool-down effects on soreness and recovery</t>
         </is>
       </c>
     </row>
     <row r="14" ht="86" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>sleep_habits</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>NHLBI — Healthy Sleep Habits</t>
+          <t>Kellmann et al. (2018) — Recovery and Performance in Sport: Consensus Statement</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>https://www.nhlbi.nih.gov/health/sleep-deprivation/healthy-sleep-habits</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29345524/</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>Public health guidance</t>
+          <t>Consensus statement</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>Thói quen ngủ và lịch sinh hoạt</t>
+          <t>Phục hồi cần cá nhân hóa, gồm tải tập và áp lực cuộc sống</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>Sleep habits and consistent schedules</t>
+          <t>Individual recovery, training load and life demands</t>
         </is>
       </c>
     </row>
     <row r="15" ht="86" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>testosterone</t>
+          <t>dorey_trial</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Bhasin et al. (2018) — Testosterone Therapy in Men With Hypogonadism: An Endocrine Society Clinical Practice Guideline</t>
+          <t>Dorey et al. (2004) — Randomised controlled trial of pelvic floor muscle exercises and manometric biofeedback for erectile dysfunction</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/29562364/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/15527607/</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Clinical practice guideline</t>
+          <t>Randomized controlled trial</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>Triệu chứng cộng xét nghiệm buổi sáng lặp lại; tránh testosterone khi muốn có con</t>
+          <t>Tập sàn chậu kết hợp biofeedback và lối sống ở 55 nam giới có ED; không phải thử nghiệm app đơn lẻ</t>
         </is>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>Symptoms plus repeated morning tests; avoid testosterone when planning fertility</t>
+          <t>Combined pelvic-floor training, biofeedback and lifestyle advice in 55 men with ED; not a stand-alone app trial</t>
         </is>
       </c>
     </row>
     <row r="16" ht="86" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>male_fertility</t>
+          <t>pastore_study</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>AUA/ASRM — Diagnosis and treatment of infertility in men: guideline part II</t>
+          <t>Pastore et al. (2014) — Pelvic floor muscle rehabilitation for patients with lifelong premature ejaculation: a novel therapeutic approach</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>https://integration.asrm.org/practice-guidance/practice-committee-documents/diagnosis-and-treatment-of-infertility-in-men-aua-asrm-guideline-part2/</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/24883105/</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>Clinical practice guideline</t>
+          <t>Small uncontrolled intervention study</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>Giới hạn bằng chứng của chất bổ sung và tác động testosterone đến sinh sản</t>
+          <t>Chương trình phục hồi 12 tuần ở 40 người; kết quả hứa hẹn với giới hạn thiết kế</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Limited supplement evidence and testosterone-related fertility concerns</t>
+          <t>Twelve-week rehabilitation in 40 men; promising findings with design limitations</t>
         </is>
       </c>
     </row>
     <row r="17" ht="86" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>sleep_t</t>
+          <t>ejaculation</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Leproult &amp; Van Cauter (2011) — Effect of 1 week of sleep restriction on testosterone levels in young healthy men</t>
+          <t>NHS — Ejaculation problems</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/21632481/</t>
+          <t>https://www.nhs.uk/conditions/ejaculation-problems/</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>Small experimental study</t>
+          <t>Public health guidance</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>Thử nghiệm nhỏ ở nam trẻ; không quy đổi thiếu ngủ thành tuổi già</t>
+          <t>Các rối loạn xuất tinh và lựa chọn điều trị</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Small study in young men; does not translate sleep loss into years of ageing</t>
+          <t>Ejaculatory difficulties and treatment options</t>
         </is>
       </c>
     </row>
     <row r="18" ht="86" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>sleep_length</t>
+          <t>libido</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>NHLBI — How Much Sleep Is Enough?</t>
+          <t>NHS — Low sex drive (loss of libido)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>https://www.nhlbi.nih.gov/health/sleep/how-much-sleep</t>
+          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -5485,61 +5485,61 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>Thời lượng ngủ theo tuổi; nợ ngủ</t>
+          <t>Nhiều yếu tố ảnh hưởng ham muốn và chăm sóc theo nguyên nhân</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>Age-related sleep needs; sleep debt</t>
+          <t>Multiple influences on desire and cause-based care</t>
         </is>
       </c>
     </row>
     <row r="19" ht="86" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>apnea</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>NHLBI — Sleep Apnea Symptoms</t>
+          <t>Mallory et al. (2019) — Couples' Sexual Communication and Dimensions of Sexual Function: A Meta-Analysis</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>https://www.nhlbi.nih.gov/health/sleep-apnea/symptoms</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/30777780/</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>Public health guidance</t>
+          <t>Meta-analysis of associations</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>Ngáy, ngưng thở và buồn ngủ ban ngày</t>
+          <t>Liên hệ giữa giao tiếp và chức năng tình dục; không chứng minh nhân quả</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>Snoring, breathing pauses and daytime sleepiness</t>
+          <t>Association of communication and sexual function; not proof of causation</t>
         </is>
       </c>
     </row>
     <row r="20" ht="86" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>libido</t>
+          <t>testicle</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>NHS — Low sex drive (loss of libido)</t>
+          <t>NHS — Testicle pain</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>https://www.nhs.uk/symptoms/loss-of-libido/</t>
+          <t>https://www.nhs.uk/symptoms/testicle-pain/</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>Nhiều yếu tố ảnh hưởng ham muốn và chăm sóc theo nguyên nhân</t>
+          <t>Đau tinh hoàn đột ngột hoặc nặng cần chăm sóc khẩn</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>Multiple influences on desire and cause-based care</t>
+          <t>Sudden or severe testicular pain requires urgent care</t>
         </is>
       </c>
     </row>
@@ -5593,261 +5593,997 @@
     <row r="22" ht="86" customHeight="1">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Mallory et al. (2019) — Couples' Sexual Communication and Dimensions of Sexual Function: A Meta-Analysis</t>
+          <t>WHO — Healthy diet</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/30777780/</t>
+          <t>https://www.who.int/news-room/fact-sheets/detail/healthy-diet</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>Meta-analysis of associations</t>
+          <t>Public health guidance</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>Liên hệ giữa giao tiếp và chức năng tình dục; không chứng minh nhân quả</t>
+          <t>Chế độ ăn đa dạng và chất lượng thực phẩm</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>Association of communication and sexual function; not proof of causation</t>
+          <t>Dietary variety and food quality</t>
         </is>
       </c>
     </row>
     <row r="23" ht="86" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>couple_sleep</t>
+          <t>hypogonadism</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>The association between couple relationships and sleep: A systematic review and meta-analysis</t>
+          <t>Endocrine Society — Hypogonadism in Men</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/39514915/</t>
+          <t>https://www.endocrine.org/patient-engagement/endocrine-library/hypogonadism</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>Systematic review and meta-analysis</t>
+          <t>Professional patient guidance</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>Liên hệ hai chiều có thể có giữa giấc ngủ và chất lượng quan hệ</t>
+          <t>Chẩn đoán thiếu testosterone và giới hạn xét nghiệm</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>Associations between sleep and relationship quality</t>
+          <t>Low testosterone diagnosis and testing limitations</t>
         </is>
       </c>
     </row>
     <row r="24" ht="86" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>zinc</t>
+          <t>reds</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>NIH ODS — Zinc: Health Professional Fact Sheet</t>
+          <t>Mountjoy et al. (2023) — IOC consensus statement on Relative Energy Deficiency in Sport (REDs)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>https://ods.od.nih.gov/factsheets/Zinc-HealthProfessional/</t>
+          <t>https://bjsm.bmj.com/content/57/17/1073</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>Evidence fact sheet</t>
+          <t>Consensus statement</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>Nhu cầu kẽm, thiếu hụt và tác hại khi dư</t>
+          <t>Thiếu năng lượng, xương, kinh nguyệt và đánh giá đa chuyên ngành</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>Zinc needs, deficiency and excess toxicity</t>
+          <t>Low energy availability, bone, menstrual health and multidisciplinary assessment</t>
         </is>
       </c>
     </row>
     <row r="25" ht="86" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>NIH ODS — Vitamin D: Fact Sheet for Consumers</t>
+          <t>WHO — Alcohol</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>https://ods.od.nih.gov/factsheets/VitaminD-Consumer/</t>
+          <t>https://www.who.int/news-room/fact-sheets/detail/alcohol</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>Evidence fact sheet</t>
+          <t>Public health evidence summary</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>Vai trò vitamin D và nguy cơ dùng quá mức</t>
+          <t>Nguy cơ sức khỏe từ rượu; không có mức uống hoàn toàn không rủi ro</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>Vitamin D roles and excessive intake risks</t>
+          <t>Alcohol-related health risks; no completely risk-free consumption</t>
         </is>
       </c>
     </row>
     <row r="26" ht="86" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>natural_fertility</t>
+          <t>testosterone</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>ASRM (2022) — Optimizing natural fertility: a committee opinion</t>
+          <t>Bhasin et al. (2018) — Testosterone Therapy in Men With Hypogonadism: An Endocrine Society Clinical Practice Guideline</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>https://integration.asrm.org/globalassets/_asrm/practice-guidance/practice-guidelines/pdf/optimizing_natural_fertility.pdf</t>
+          <t>https://pubmed.ncbi.nlm.nih.gov/29562364/</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>Committee opinion</t>
+          <t>Clinical practice guideline</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>Thời điểm quan hệ, giới hạn dự đoán và khi đánh giá hiếm muộn</t>
+          <t>Triệu chứng cộng xét nghiệm buổi sáng lặp lại; tránh testosterone khi muốn có con</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>Intercourse timing, prediction limitations and fertility evaluation</t>
+          <t>Symptoms plus repeated morning tests; avoid testosterone when planning fertility</t>
         </is>
       </c>
     </row>
     <row r="27" ht="86" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>fasting</t>
+          <t>male_fertility</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>Cienfuegos et al. (2022) — Effect of Intermittent Fasting on Reproductive Hormone Levels in Females and Males: A Review of Human Trials</t>
+          <t>AUA/ASRM — Diagnosis and treatment of infertility in men: guideline part II</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>https://pubmed.ncbi.nlm.nih.gov/35684143/</t>
+          <t>https://integration.asrm.org/practice-guidance/practice-committee-documents/diagnosis-and-treatment-of-infertility-in-men-aua-asrm-guideline-part2/</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>Review of human trials</t>
+          <t>Clinical practice guideline</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>Nghiên cứu hormone còn ít; không thể hứa tăng testosterone</t>
+          <t>Giới hạn bằng chứng của chất bổ sung và tác động testosterone đến sinh sản</t>
         </is>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>Limited hormone trials; no basis to promise a testosterone increase</t>
+          <t>Limited supplement evidence and testosterone-related fertility concerns</t>
         </is>
       </c>
     </row>
     <row r="28" ht="86" customHeight="1">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>hydration</t>
+          <t>openstax_gonadal</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>NHS — Dehydration</t>
+          <t>OpenStax Anatomy and Physiology 2e — Gonadal and Placental Hormones</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>https://www.nhs.uk/conditions/dehydration/</t>
+          <t>https://openstax.org/books/anatomy-and-physiology-2e/pages/17-8-gonadal-and-placental-hormones</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>Public health guidance</t>
+          <t>Physiology textbook</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>Dấu hiệu mất nước và khi cần chăm sóc khẩn</t>
+          <t>Điều hòa hormone sinh dục và phân biệt các chức năng tuyến sinh dục</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>Dehydration symptoms and when urgent care is needed</t>
+          <t>Gonadal hormone regulation and distinct gonadal functions</t>
         </is>
       </c>
     </row>
     <row r="29" ht="86" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
+          <t>missed</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Missed or late periods</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/symptoms/missed-or-late-periods/</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Nguyên nhân trễ kinh và thời điểm đi khám</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>Causes of missed periods and when to seek care</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="86" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>sleep_habits</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>NHLBI — Healthy Sleep Habits</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhlbi.nih.gov/health/sleep-deprivation/healthy-sleep-habits</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Thói quen ngủ và lịch sinh hoạt</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>Sleep habits and consistent schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="86" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>esposito_trial</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Esposito et al. (2004) — Effect of lifestyle changes on erectile dysfunction in obese men: a randomized controlled trial</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/15213209/</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Randomized controlled trial</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Can thiệp lối sống phối hợp ở 110 nam giới béo phì; không tách hiệu quả một thực phẩm</t>
+        </is>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>Combined lifestyle intervention in 110 obese men; not an isolated food effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="86" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>Morton et al. (2018) — A systematic review, meta-analysis and meta-regression of the effect of protein supplementation on resistance training-induced gains in muscle mass and strength in healthy adults</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/28698222/</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>Systematic review and meta-analysis</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Protein và tập kháng lực ở người khỏe mạnh; không áp dụng trực tiếp cho bệnh thận</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>Protein with resistance training in healthy adults; not directly applicable to kidney disease</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="86" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>NIH ODS — Zinc: Health Professional Fact Sheet</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>https://ods.od.nih.gov/factsheets/Zinc-HealthProfessional/</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>Evidence fact sheet</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>Nhu cầu kẽm, thiếu hụt và tác hại khi dư</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>Zinc needs, deficiency and excess toxicity</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="86" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>vitamin_d</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>NIH ODS — Vitamin D: Fact Sheet for Consumers</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>https://ods.od.nih.gov/factsheets/VitaminD-Consumer/</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>Evidence fact sheet</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Vai trò vitamin D và nguy cơ dùng quá mức</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>Vitamin D roles and excessive intake risks</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="86" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>sleep_stages</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>NHLBI — Sleep Phases and Stages</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhlbi.nih.gov/health/sleep/stages-of-sleep</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>NREM, REM và thay đổi theo tuổi</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>NREM, REM and age-related variation</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="86" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>sleep_tech</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>Schutte-Rodin et al. (2021) — Evaluating consumer and clinical sleep technologies: an American Academy of Sleep Medicine update</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/34314344/</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Professional society review</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>Giới hạn đánh giá và xác thực công nghệ theo dõi giấc ngủ</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>Evaluation and validation limits of sleep technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="86" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>pulse</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>American Heart Association — All About Heart Rate</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>https://www.heart.org/en/health-topics/high-blood-pressure/the-facts-about-high-blood-pressure/all-about-heart-rate-pulse</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Professional patient guidance</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>Nhịp tim nghỉ, yếu tố ảnh hưởng và triệu chứng cần khám</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="inlineStr">
+        <is>
+          <t>Resting pulse, influencing factors and warning symptoms</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="86" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>fitness</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Ross et al. (2016) — Importance of Assessing Cardiorespiratory Fitness in Clinical Practice</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/27881567/</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>AHA scientific statement</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>Thể lực tim phổi và đánh giá nguy cơ sức khỏe</t>
+        </is>
+      </c>
+      <c r="F38" s="19" t="inlineStr">
+        <is>
+          <t>Cardiorespiratory fitness and health risk assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="86" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>sleep_t</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>Leproult &amp; Van Cauter (2011) — Effect of 1 week of sleep restriction on testosterone levels in young healthy men</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/21632481/</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Small experimental study</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>Thử nghiệm nhỏ ở nam trẻ; không quy đổi thiếu ngủ thành tuổi già</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>Small study in young men; does not translate sleep loss into years of ageing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="86" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>sleep_length</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>NHLBI — How Much Sleep Is Enough?</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhlbi.nih.gov/health/sleep/how-much-sleep</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>Thời lượng ngủ theo tuổi; nợ ngủ</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>Age-related sleep needs; sleep debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="86" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>apnea</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>NHLBI — Sleep Apnea Symptoms</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhlbi.nih.gov/health/sleep-apnea/symptoms</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>Ngáy, ngưng thở và buồn ngủ ban ngày</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>Snoring, breathing pauses and daytime sleepiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="86" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>sleep_clock</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>NHLBI — Your Sleep/Wake Cycle</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhlbi.nih.gov/health/sleep/sleep-wake-cycle</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Nhịp sinh học, ánh sáng và áp lực ngủ</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>Circadian timing, light and sleep pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="86" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>device_stress</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Google — Find out what data Fitbit collects for Fitbit account users</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>https://support.google.com/product-documentation/answer/14779613?hl=en</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Manufacturer documentation</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Các loại dữ liệu, điện dẫn da và điểm stress trên từng thiết bị</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>Device-specific data types, EDA and stress scores</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="86" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>gottman_ratio</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>The Gottman Institute — The Magic Relationship Ratio, According to Science</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>https://www.gottman.com/blog/the-magic-relationship-ratio-according-science/</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>First-party explanation of an observational relationship model</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>Nguồn của mô hình 5:1; không phải ngưỡng chẩn đoán hoặc công thức bảo đảm quan hệ</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
+        <is>
+          <t>Origin of the 5:1 model; not a diagnostic threshold or guaranteed relationship formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="86" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>couple_sleep</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>The association between couple relationships and sleep: A systematic review and meta-analysis</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39514915/</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Systematic review and meta-analysis</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Liên hệ hai chiều có thể có giữa giấc ngủ và chất lượng quan hệ</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
+          <t>Associations between sleep and relationship quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="86" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>natural_fertility</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>ASRM (2022) — Optimizing natural fertility: a committee opinion</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>https://integration.asrm.org/globalassets/_asrm/practice-guidance/practice-guidelines/pdf/optimizing_natural_fertility.pdf</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>Committee opinion</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>Thời điểm quan hệ, giới hạn dự đoán và khi đánh giá hiếm muộn</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="inlineStr">
+        <is>
+          <t>Intercourse timing, prediction limitations and fertility evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="86" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>semen_who</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>WHO (2021) — WHO laboratory manual for the examination and processing of human semen, sixth edition</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>https://www.who.int/publications/i/item/9789240030787/</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Laboratory manual</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>Quy trình xét nghiệm và giới hạn diễn giải thông số tinh dịch</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>Laboratory procedures and limits of semen-parameter interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="86" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>fasting</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>Cienfuegos et al. (2022) — Effect of Intermittent Fasting on Reproductive Hormone Levels in Females and Males: A Review of Human Trials</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35684143/</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>Review of human trials</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>Nghiên cứu hormone còn ít; không thể hứa tăng testosterone</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
+        <is>
+          <t>Limited hormone trials; no basis to promise a testosterone increase</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="86" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>hydration</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>NHS — Dehydration</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>https://www.nhs.uk/conditions/dehydration/</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>Dấu hiệu mất nước và khi cần chăm sóc khẩn</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>Dehydration symptoms and when urgent care is needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="86" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>intensity</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>CDC — Measuring Physical Activity Intensity</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/physicalactivity/basics/measuring/index.html</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>Public health guidance</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>Talk test phân biệt vận động vừa và mạnh</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
+          <t>Talk test for moderate and vigorous activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="86" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
           <t>activity</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>WHO — Physical activity</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>https://www.who.int/news-room/fact-sheets/detail/physical-activity</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>Public health guideline summary</t>
         </is>
       </c>
-      <c r="E29" s="19" t="inlineStr">
+      <c r="E51" s="19" t="inlineStr">
         <is>
           <t>Khuyến nghị vận động theo nhóm đối tượng</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>Activity recommendations by population</t>
         </is>
       </c>
     </row>
+    <row r="52" ht="86" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>abstinence_retracted</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>Jiang et al. (2003) — A research on the relationship between ejaculation and serum testosterone level in men [RETRACTED]</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/12659241/</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>Retracted paper — cited only to explain exclusion</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>Chỉ dẫn để giải thích vì sao loại bỏ lời khuyên dựa trên nghiên cứu đã thu hồi; không dùng làm bằng chứng hiệu quả</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t>Cited only to explain exclusion of an abstinence claim; not efficacy evidence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F29"/>
+  <autoFilter ref="A1:F52"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -5877,6 +6613,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
